--- a/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Point Performance Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CDFF5C-5D71-472B-8571-61FCB74D1901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BB12A5-E68C-4159-AD47-B29EA5043A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2796" yWindow="708" windowWidth="18684" windowHeight="10992" activeTab="4" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
@@ -517,25 +517,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="75">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="72">
     <dxf>
       <font>
         <b/>
@@ -2314,80 +2296,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}" name="Table3" displayName="Table3" ref="A1:K200" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}" name="Table3" displayName="Table3" ref="A1:K200" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" tableBorderDxfId="55">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F919674C-10DC-DE44-A9F3-90B3D200DA5E}" name="Requirement #" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{CBE9135E-D43C-B64F-82F2-4030E55EBC51}" name="Requirement Type" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{41824150-61A9-7E43-BA0E-0D841F02D9D0}" name="Input 1" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{2CB221DF-97B6-3A4B-AA29-385AAD8EC923}" name="Input 2" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{8A52CDC3-99A4-6F43-8D92-A339D636927D}" name="Input 3" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{14091491-0BCB-3A45-9BC5-4515396CA540}" name="Input 4" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{3E4C5F17-B6DA-944B-9CFE-147012A5B23F}" name="Input 5" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{C85697CD-6A76-EB47-A95B-AE2F7873920E}" name="Input 6" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{818CDA49-0E39-2946-8757-A9D15E8D4A6E}" name="Input 7" dataDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{3F0DAC1D-EB2F-FC4C-AEEC-B9F4795484F8}" name="Input 8" dataDxfId="48"/>
-    <tableColumn id="11" xr3:uid="{34AA4A8F-2A21-874E-9EAF-8ECBDCA330CB}" name="Input 9" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{F919674C-10DC-DE44-A9F3-90B3D200DA5E}" name="Requirement #" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{CBE9135E-D43C-B64F-82F2-4030E55EBC51}" name="Requirement Type" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{41824150-61A9-7E43-BA0E-0D841F02D9D0}" name="Input 1" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{2CB221DF-97B6-3A4B-AA29-385AAD8EC923}" name="Input 2" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{8A52CDC3-99A4-6F43-8D92-A339D636927D}" name="Input 3" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{14091491-0BCB-3A45-9BC5-4515396CA540}" name="Input 4" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{3E4C5F17-B6DA-944B-9CFE-147012A5B23F}" name="Input 5" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{C85697CD-6A76-EB47-A95B-AE2F7873920E}" name="Input 6" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{818CDA49-0E39-2946-8757-A9D15E8D4A6E}" name="Input 7" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{3F0DAC1D-EB2F-FC4C-AEEC-B9F4795484F8}" name="Input 8" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{34AA4A8F-2A21-874E-9EAF-8ECBDCA330CB}" name="Input 9" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" tableBorderDxfId="41">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73" tableBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70" tableBorderDxfId="69">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="66"/>
-    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="65"/>
-    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="64"/>
-    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="63"/>
-    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="62"/>
-    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3041,12 +3023,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:I6">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J4 B7:J14">
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5982,17 +5964,17 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD5 L6:XFD17 B8:K15 F17:K17 B18:XFD21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="13" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:I7">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8894,17 +8876,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD3 J4:XFD4 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11806,17 +11788,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD4 C5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12094,7 +12076,9 @@
       <c r="E9" s="3">
         <v>0.6</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
       <c r="G9" s="3" t="s">
         <v>18</v>
       </c>
@@ -12158,7 +12142,9 @@
       <c r="E11" s="3">
         <v>0.49</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
       <c r="G11" s="3" t="s">
         <v>18</v>
       </c>
@@ -12222,7 +12208,9 @@
       <c r="E13" s="3">
         <v>0.49</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3">
+        <v>2</v>
+      </c>
       <c r="G13" s="3" t="s">
         <v>18</v>
       </c>
@@ -12286,7 +12274,9 @@
       <c r="E15" s="3">
         <v>0.8</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
       <c r="G15" s="3" t="s">
         <v>18</v>
       </c>
@@ -14709,8 +14699,8 @@
       <c r="K200" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:XFD1 B16:XFD21 A22:XFD1048576 L2:XFD15">
-    <cfRule type="expression" dxfId="7" priority="8">
+  <conditionalFormatting sqref="A1:B1 D1:XFD1 L2:XFD15 B16:XFD21 A22:XFD1048576">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14719,18 +14709,18 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:K2 C8:K8 C10:K10 D9:K9 C12:K12 D11:K11 C14:K14 D13:K13 D15:K15 C4:K4 C3:G3 I3:K3 C5:F5 H5:K5">
+  <conditionalFormatting sqref="C2:K2 C3:G3 I3:K3 C4:K4 C5:F5 H5:K5 C8:K8 D9:K9 C10:K10 D11:K11 C12:K12 D13:K13 C14:K14 D15:K15">
     <cfRule type="expression" dxfId="2" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="G5">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="H3">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="52">
   <si>
     <t xml:space="preserve">Takeoff Distance</t>
   </si>
@@ -161,10 +161,13 @@
     <t xml:space="preserve">Takeoff </t>
   </si>
   <si>
-    <t xml:space="preserve">TO Distance 3.5kft</t>
+    <t xml:space="preserve">TO Distance 2.5kft</t>
   </si>
   <si>
-    <t xml:space="preserve">Landing Distance 3.2kft</t>
+    <t xml:space="preserve">Landing Distance 3.6kft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stall Velocity 120kts</t>
   </si>
   <si>
     <t xml:space="preserve">Abs Ceiling 45kft</t>
@@ -475,100 +478,52 @@
   </cellStyles>
   <dxfs count="16">
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="1"/>
-        <i val="0"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
     </dxf>
   </dxfs>
   <colors>
@@ -9877,7 +9832,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.29"/>
@@ -9954,7 +9909,7 @@
       </c>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="n">
@@ -9976,7 +9931,7 @@
         <v>0.035</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>45</v>
@@ -10024,7 +9979,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0.2</v>
@@ -10033,7 +9988,7 @@
         <v>0.035</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>46</v>
@@ -10066,20 +10021,20 @@
       <c r="J6" s="8"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -10132,7 +10087,7 @@
         <v>45000</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>1</v>
@@ -10150,7 +10105,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10188,7 +10143,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6" t="n">
@@ -10198,7 +10153,7 @@
         <v>35000</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>1</v>
@@ -10216,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10254,7 +10209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6" t="n">
@@ -10264,7 +10219,7 @@
         <v>25000</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>3</v>
@@ -10282,7 +10237,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10348,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12767,7 +12722,7 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:K2 C3:G3 I3:K3 C4:K4 C5:F5 H5:K5 C8:K8 D9:K9 C10:K10 D11:K11 C12:K12 D13:K13 C14:K14 D15:K15">
+  <conditionalFormatting sqref="C2:K2 C3:G3 I3:K3 C4:K4 C5:F5 H5:K5 C8:K8 D9:K9 C10:K10 C12:K12 C14:K14 D15:K15 D11:K11 D13:K13">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Point Performance Requirements\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11288B4F-D637-47D1-BE8E-AE342F082457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Templates" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="F16" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="C172" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="B747" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="JetSubmersible" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Templates" sheetId="1" r:id="rId1"/>
+    <sheet name="F16" sheetId="2" r:id="rId2"/>
+    <sheet name="C172" sheetId="3" r:id="rId3"/>
+    <sheet name="B747" sheetId="4" r:id="rId4"/>
+    <sheet name="JetSubmersible" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,191 +42,173 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="52">
   <si>
-    <t xml:space="preserve">Takeoff Distance</t>
+    <t>Takeoff Distance</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta</t>
+    <t>Beta</t>
   </si>
   <si>
-    <t xml:space="preserve">Altitude [ft]</t>
+    <t>Altitude [ft]</t>
   </si>
   <si>
-    <t xml:space="preserve">Throttle</t>
+    <t>Throttle</t>
   </si>
   <si>
-    <t xml:space="preserve">CL Max</t>
+    <t>CL Max</t>
   </si>
   <si>
-    <t xml:space="preserve">Coef Friction</t>
+    <t>Coef Friction</t>
   </si>
   <si>
-    <t xml:space="preserve">CDx</t>
+    <t>CDx</t>
   </si>
   <si>
-    <t xml:space="preserve">Takeoff Distance [ft]</t>
+    <t>Takeoff Distance [ft]</t>
   </si>
   <si>
-    <t xml:space="preserve">Label</t>
+    <t>Label</t>
   </si>
   <si>
-    <t xml:space="preserve">Landing Distance</t>
+    <t>Landing Distance</t>
   </si>
   <si>
-    <t xml:space="preserve">Landing Distance [ft]</t>
+    <t>Landing Distance [ft]</t>
   </si>
   <si>
-    <t xml:space="preserve">Stall Velocity</t>
+    <t>Stall Velocity</t>
   </si>
   <si>
-    <t xml:space="preserve">Stall Velocity [kts]</t>
+    <t>Stall Velocity [kts]</t>
   </si>
   <si>
-    <t xml:space="preserve">Absolute Ceiling</t>
+    <t>Absolute Ceiling</t>
   </si>
   <si>
     <t xml:space="preserve">Mach </t>
   </si>
   <si>
-    <t xml:space="preserve">n</t>
+    <t>n</t>
   </si>
   <si>
-    <t xml:space="preserve">Rate of Climb [ft/s]</t>
+    <t>Rate of Climb [ft/s]</t>
   </si>
   <si>
-    <t xml:space="preserve">Acceleration [ft/s^2]</t>
+    <t>Acceleration [ft/s^2]</t>
   </si>
   <si>
-    <t xml:space="preserve">Cdx</t>
+    <t>Cdx</t>
   </si>
   <si>
-    <t xml:space="preserve">Service Ceiling</t>
+    <t>Service Ceiling</t>
   </si>
   <si>
-    <t xml:space="preserve">Sustained Turn</t>
+    <t>Sustained Turn</t>
   </si>
   <si>
-    <t xml:space="preserve">Max Mach</t>
+    <t>Max Mach</t>
   </si>
   <si>
-    <t xml:space="preserve">VTOL</t>
+    <t>VTOL</t>
   </si>
   <si>
-    <t xml:space="preserve">Altitude[ft]</t>
+    <t>Altitude[ft]</t>
   </si>
   <si>
-    <t xml:space="preserve">V_Climb [ft/s]</t>
+    <t>V_Climb [ft/s]</t>
   </si>
   <si>
-    <t xml:space="preserve">Requirement #</t>
+    <t>Requirement #</t>
   </si>
   <si>
-    <t xml:space="preserve">Requirement Type</t>
+    <t>Requirement Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 1</t>
+    <t>Input 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 2</t>
+    <t>Input 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 3</t>
+    <t>Input 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 4</t>
+    <t>Input 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 5</t>
+    <t>Input 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 6</t>
+    <t>Input 6</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 7</t>
+    <t>Input 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 8</t>
+    <t>Input 8</t>
   </si>
   <si>
-    <t xml:space="preserve">Input 9</t>
+    <t>Input 9</t>
   </si>
   <si>
-    <t xml:space="preserve">MIL</t>
+    <t>MIL</t>
   </si>
   <si>
-    <t xml:space="preserve">TO A</t>
+    <t>TO A</t>
   </si>
   <si>
-    <t xml:space="preserve">TO B</t>
+    <t>TO B</t>
   </si>
   <si>
     <t xml:space="preserve">Landing </t>
   </si>
   <si>
-    <t xml:space="preserve">AB</t>
+    <t>AB</t>
   </si>
   <si>
-    <t xml:space="preserve">PROP</t>
+    <t>PROP</t>
   </si>
   <si>
-    <t xml:space="preserve">Takeoff</t>
+    <t>Takeoff</t>
   </si>
   <si>
-    <t xml:space="preserve">Landing</t>
+    <t>Landing</t>
   </si>
   <si>
     <t xml:space="preserve">Takeoff </t>
   </si>
   <si>
-    <t xml:space="preserve">TO Distance 2.5kft</t>
+    <t>TO Distance 2.5kft</t>
   </si>
   <si>
-    <t xml:space="preserve">Landing Distance 3.6kft</t>
+    <t>Abs Ceiling 45kft</t>
   </si>
   <si>
-    <t xml:space="preserve">Stall Velocity 120kts</t>
+    <t>Service Ceiling 35kft</t>
   </si>
   <si>
-    <t xml:space="preserve">Abs Ceiling 45kft</t>
+    <t>Sustained Turn 25kft</t>
   </si>
   <si>
-    <t xml:space="preserve">Service Ceiling 35kft</t>
+    <t>Landing Distance 1kft</t>
   </si>
   <si>
-    <t xml:space="preserve">Sustained Turn 25kft</t>
+    <t>Max Mach (0.95) @ 35kft</t>
   </si>
   <si>
-    <t xml:space="preserve">Max Mach 35kft</t>
+    <t>Stall Velocity 115kts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -220,7 +218,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
@@ -243,289 +241,280 @@
     </fill>
   </fills>
   <borders count="15">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
-      <top style="medium"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="medium"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -584,104 +573,436 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table3" displayName="Table3" ref="A1:K200" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:K200" totalsRowShown="0">
+  <autoFilter ref="A1:K200" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="Requirement #"/>
-    <tableColumn id="2" name="Requirement Type"/>
-    <tableColumn id="3" name="Input 1"/>
-    <tableColumn id="4" name="Input 2"/>
-    <tableColumn id="5" name="Input 3"/>
-    <tableColumn id="6" name="Input 4"/>
-    <tableColumn id="7" name="Input 5"/>
-    <tableColumn id="8" name="Input 6"/>
-    <tableColumn id="9" name="Input 7"/>
-    <tableColumn id="10" name="Input 8"/>
-    <tableColumn id="11" name="Input 9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Requirement #"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Requirement Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Input 1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Input 2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Input 3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Input 4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Input 5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Input 6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Input 7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Input 8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Input 9"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table32" displayName="Table32" ref="A1:K200" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0">
+  <autoFilter ref="A1:K200" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="Requirement #"/>
-    <tableColumn id="2" name="Requirement Type"/>
-    <tableColumn id="3" name="Input 1"/>
-    <tableColumn id="4" name="Input 2"/>
-    <tableColumn id="5" name="Input 3"/>
-    <tableColumn id="6" name="Input 4"/>
-    <tableColumn id="7" name="Input 5"/>
-    <tableColumn id="8" name="Input 6"/>
-    <tableColumn id="9" name="Input 7"/>
-    <tableColumn id="10" name="Input 8"/>
-    <tableColumn id="11" name="Input 9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Requirement #"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Requirement Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Input 1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Input 2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Input 3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Input 4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Input 5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Input 6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Input 7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Input 8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Input 9"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table323" displayName="Table323" ref="A1:K200" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0">
+  <autoFilter ref="A1:K200" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="Requirement #"/>
-    <tableColumn id="2" name="Requirement Type"/>
-    <tableColumn id="3" name="Input 1"/>
-    <tableColumn id="4" name="Input 2"/>
-    <tableColumn id="5" name="Input 3"/>
-    <tableColumn id="6" name="Input 4"/>
-    <tableColumn id="7" name="Input 5"/>
-    <tableColumn id="8" name="Input 6"/>
-    <tableColumn id="9" name="Input 7"/>
-    <tableColumn id="10" name="Input 8"/>
-    <tableColumn id="11" name="Input 9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Requirement #"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Requirement Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Input 1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Input 2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Input 3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Input 4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Input 5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Input 6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Input 7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Input 8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Input 9"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table325" displayName="Table325" ref="A1:K200" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0">
+  <autoFilter ref="A1:K200" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="Requirement #"/>
-    <tableColumn id="2" name="Requirement Type"/>
-    <tableColumn id="3" name="Input 1"/>
-    <tableColumn id="4" name="Input 2"/>
-    <tableColumn id="5" name="Input 3"/>
-    <tableColumn id="6" name="Input 4"/>
-    <tableColumn id="7" name="Input 5"/>
-    <tableColumn id="8" name="Input 6"/>
-    <tableColumn id="9" name="Input 7"/>
-    <tableColumn id="10" name="Input 8"/>
-    <tableColumn id="11" name="Input 9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Requirement #"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Requirement Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Input 1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Input 2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Input 3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Input 4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Input 5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Input 6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Input 7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Input 8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Input 9"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AMK22"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="20.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="13.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="10" style="1" width="10.8"/>
+    <col min="1" max="4" width="20.796875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.19921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.69921875" style="1" customWidth="1"/>
+    <col min="10" max="1025" width="10.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -711,7 +1032,7 @@
       </c>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -723,7 +1044,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:10">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
@@ -751,7 +1072,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:10">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -763,7 +1084,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:10">
       <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
@@ -785,7 +1106,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:10">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -797,7 +1118,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" s="9" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:10" s="9" customFormat="1">
       <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
@@ -829,7 +1150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:10">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -841,7 +1162,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" s="9" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:10" s="9" customFormat="1">
       <c r="A9" s="7" t="s">
         <v>19</v>
       </c>
@@ -873,7 +1194,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:10">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -885,7 +1206,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" s="9" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:10" s="9" customFormat="1">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
@@ -917,7 +1238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:10">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -929,7 +1250,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" s="9" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:10" s="9" customFormat="1">
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
@@ -961,7 +1282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:10">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -973,7 +1294,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
         <v>22</v>
       </c>
@@ -987,62 +1308,54 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:10">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
     </row>
-    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
     </row>
-    <row r="22" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:2">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:I6">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J4 B7:J14">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K200"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AMK200"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="27.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="1" width="10.8"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.09765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5" style="1" customWidth="1"/>
+    <col min="12" max="1025" width="10.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11">
       <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
@@ -1077,8 +1390,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="n">
+    <row r="2" spans="1:11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -1110,28 +1423,28 @@
       </c>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="6">
         <v>0</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="6">
         <v>1.2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="6">
         <v>0.02</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I3" s="13" t="n">
+      <c r="H3" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I3" s="13">
         <v>3500</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1139,8 +1452,8 @@
       </c>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -1172,28 +1485,28 @@
       </c>
       <c r="K4" s="14"/>
     </row>
-    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6">
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="6">
         <v>1.2</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="6">
         <v>0.02</v>
       </c>
-      <c r="H5" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I5" s="13" t="n">
+      <c r="H5" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I5" s="13">
         <v>4000</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -1201,8 +1514,8 @@
       </c>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+    <row r="6" spans="1:11">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -1232,25 +1545,25 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="6">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6">
         <v>0</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="6">
         <v>0.4</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="6">
         <v>1.2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="6">
         <v>0.05</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="6">
         <v>4500</v>
       </c>
       <c r="I7" s="13" t="s">
@@ -1259,8 +1572,8 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+    <row r="8" spans="1:11">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1284,16 +1597,16 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:11">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="6">
         <v>5000</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="6">
         <v>1.5</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="6">
         <v>160</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -1305,8 +1618,8 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+    <row r="10" spans="1:11">
+      <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1340,39 +1653,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:11">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="C11" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D11" s="6">
         <v>40000</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="6">
         <v>0.8</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="6">
         <v>1</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="6">
         <v>0</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="6">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="6">
         <v>0</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+    <row r="12" spans="1:11">
+      <c r="A12" s="5">
         <v>6</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1406,39 +1719,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:11">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="C13" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D13" s="6">
         <v>35000</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="6">
         <v>0.8</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="6">
         <v>1</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="6">
         <v>1.67</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="6">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="6">
         <v>0</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+    <row r="14" spans="1:11">
+      <c r="A14" s="5">
         <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1472,39 +1785,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:11">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D15" s="6" t="n">
+      <c r="C15" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D15" s="6">
         <v>20000</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="6">
         <v>0.9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="6">
         <v>5</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="6">
         <v>0</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="6">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="6">
         <v>0</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+    <row r="16" spans="1:11">
+      <c r="A16" s="5">
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -1538,38 +1851,38 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:11">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D17" s="6" t="n">
+      <c r="C17" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D17" s="6">
         <v>20000</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="6">
         <v>1</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="6">
         <v>1</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="6">
         <v>0</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="13">
         <v>0</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="6">
         <v>0</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:11">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1582,7 +1895,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="14"/>
     </row>
-    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1595,7 +1908,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="14"/>
     </row>
-    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1608,7 +1921,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="14"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:11">
       <c r="A21" s="17"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1621,7 +1934,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="14"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:11">
       <c r="A22" s="17"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1634,7 +1947,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="14"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:11">
       <c r="A23" s="17"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1647,7 +1960,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="14"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:11">
       <c r="A24" s="17"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1660,7 +1973,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:11">
       <c r="A25" s="17"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1673,7 +1986,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="14"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:11">
       <c r="A26" s="17"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1686,7 +1999,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="14"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:11">
       <c r="A27" s="17"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1699,7 +2012,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:11">
       <c r="A28" s="17"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1712,7 +2025,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:11">
       <c r="A29" s="17"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1725,7 +2038,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="14"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:11">
       <c r="A30" s="17"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1738,7 +2051,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="14"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:11">
       <c r="A31" s="17"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1751,7 +2064,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="14"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:11">
       <c r="A32" s="17"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1764,7 +2077,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="14"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:11">
       <c r="A33" s="17"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1777,7 +2090,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="14"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:11">
       <c r="A34" s="17"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1790,7 +2103,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="14"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:11">
       <c r="A35" s="17"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1803,7 +2116,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="14"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:11">
       <c r="A36" s="17"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1816,7 +2129,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="14"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:11">
       <c r="A37" s="17"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1829,7 +2142,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="14"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:11">
       <c r="A38" s="17"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1842,7 +2155,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="14"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:11">
       <c r="A39" s="17"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1855,7 +2168,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="14"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:11">
       <c r="A40" s="17"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1868,7 +2181,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="14"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:11">
       <c r="A41" s="17"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1881,7 +2194,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="14"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:11">
       <c r="A42" s="17"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1894,7 +2207,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="14"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:11">
       <c r="A43" s="17"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1907,7 +2220,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="14"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:11">
       <c r="A44" s="17"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1920,7 +2233,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="14"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:11">
       <c r="A45" s="17"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1933,7 +2246,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="14"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:11">
       <c r="A46" s="17"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1946,7 +2259,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="14"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:11">
       <c r="A47" s="17"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1959,7 +2272,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="14"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:11">
       <c r="A48" s="17"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1972,7 +2285,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="14"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:11">
       <c r="A49" s="17"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1985,7 +2298,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="14"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:11">
       <c r="A50" s="17"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1998,7 +2311,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="14"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:11">
       <c r="A51" s="17"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2011,7 +2324,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="14"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:11">
       <c r="A52" s="17"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -2024,7 +2337,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="14"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:11">
       <c r="A53" s="17"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -2037,7 +2350,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="14"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:11">
       <c r="A54" s="17"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -2050,7 +2363,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="14"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:11">
       <c r="A55" s="17"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -2063,7 +2376,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="14"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:11">
       <c r="A56" s="17"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -2076,7 +2389,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="14"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:11">
       <c r="A57" s="17"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -2089,7 +2402,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="14"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:11">
       <c r="A58" s="17"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -2102,7 +2415,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="14"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:11">
       <c r="A59" s="17"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -2115,7 +2428,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="14"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:11">
       <c r="A60" s="17"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -2128,7 +2441,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="14"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:11">
       <c r="A61" s="17"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2141,7 +2454,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="14"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:11">
       <c r="A62" s="17"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2154,7 +2467,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="14"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:11">
       <c r="A63" s="17"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2167,7 +2480,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="14"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:11">
       <c r="A64" s="17"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2180,7 +2493,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="14"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:11">
       <c r="A65" s="17"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -2193,7 +2506,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="14"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:11">
       <c r="A66" s="17"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -2206,7 +2519,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="14"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:11">
       <c r="A67" s="17"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -2219,7 +2532,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="14"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:11">
       <c r="A68" s="17"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -2232,7 +2545,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="14"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:11">
       <c r="A69" s="17"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -2245,7 +2558,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:11">
       <c r="A70" s="17"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -2258,7 +2571,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="14"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:11">
       <c r="A71" s="17"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -2271,7 +2584,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:11">
       <c r="A72" s="17"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -2284,7 +2597,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="14"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:11">
       <c r="A73" s="17"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -2297,7 +2610,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="14"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:11">
       <c r="A74" s="17"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -2310,7 +2623,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="14"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:11">
       <c r="A75" s="17"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2323,7 +2636,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="14"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:11">
       <c r="A76" s="17"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -2336,7 +2649,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="14"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:11">
       <c r="A77" s="17"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -2349,7 +2662,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="14"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:11">
       <c r="A78" s="17"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -2362,7 +2675,7 @@
       <c r="J78" s="6"/>
       <c r="K78" s="14"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:11">
       <c r="A79" s="17"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -2375,7 +2688,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="14"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:11">
       <c r="A80" s="17"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -2388,7 +2701,7 @@
       <c r="J80" s="6"/>
       <c r="K80" s="14"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:11">
       <c r="A81" s="17"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -2401,7 +2714,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="14"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:11">
       <c r="A82" s="17"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -2414,7 +2727,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="14"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:11">
       <c r="A83" s="17"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -2427,7 +2740,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="14"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:11">
       <c r="A84" s="17"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -2440,7 +2753,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="14"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:11">
       <c r="A85" s="17"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -2453,7 +2766,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="14"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:11">
       <c r="A86" s="17"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -2466,7 +2779,7 @@
       <c r="J86" s="6"/>
       <c r="K86" s="14"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:11">
       <c r="A87" s="17"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2479,7 +2792,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="14"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:11">
       <c r="A88" s="17"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2492,7 +2805,7 @@
       <c r="J88" s="6"/>
       <c r="K88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:11">
       <c r="A89" s="17"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2505,7 +2818,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="14"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:11">
       <c r="A90" s="17"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2518,7 +2831,7 @@
       <c r="J90" s="6"/>
       <c r="K90" s="14"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:11">
       <c r="A91" s="17"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2531,7 +2844,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="14"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:11">
       <c r="A92" s="17"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2544,7 +2857,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="14"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:11">
       <c r="A93" s="17"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2557,7 +2870,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="14"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:11">
       <c r="A94" s="17"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2570,7 +2883,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="14"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:11">
       <c r="A95" s="17"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2583,7 +2896,7 @@
       <c r="J95" s="6"/>
       <c r="K95" s="14"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:11">
       <c r="A96" s="17"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -2596,7 +2909,7 @@
       <c r="J96" s="6"/>
       <c r="K96" s="14"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:11">
       <c r="A97" s="17"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -2609,7 +2922,7 @@
       <c r="J97" s="6"/>
       <c r="K97" s="14"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:11">
       <c r="A98" s="17"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -2622,7 +2935,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="14"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:11">
       <c r="A99" s="17"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -2635,7 +2948,7 @@
       <c r="J99" s="6"/>
       <c r="K99" s="14"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:11">
       <c r="A100" s="17"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -2648,7 +2961,7 @@
       <c r="J100" s="6"/>
       <c r="K100" s="14"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:11">
       <c r="A101" s="17"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -2661,7 +2974,7 @@
       <c r="J101" s="6"/>
       <c r="K101" s="14"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:11">
       <c r="A102" s="17"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -2674,7 +2987,7 @@
       <c r="J102" s="6"/>
       <c r="K102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:11">
       <c r="A103" s="17"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -2687,7 +3000,7 @@
       <c r="J103" s="6"/>
       <c r="K103" s="14"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:11">
       <c r="A104" s="17"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -2700,7 +3013,7 @@
       <c r="J104" s="6"/>
       <c r="K104" s="14"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:11">
       <c r="A105" s="17"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -2713,7 +3026,7 @@
       <c r="J105" s="6"/>
       <c r="K105" s="14"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:11">
       <c r="A106" s="17"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -2726,7 +3039,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="14"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:11">
       <c r="A107" s="17"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -2739,7 +3052,7 @@
       <c r="J107" s="6"/>
       <c r="K107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:11">
       <c r="A108" s="17"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -2752,7 +3065,7 @@
       <c r="J108" s="6"/>
       <c r="K108" s="14"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:11">
       <c r="A109" s="17"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -2765,7 +3078,7 @@
       <c r="J109" s="6"/>
       <c r="K109" s="14"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:11">
       <c r="A110" s="17"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -2778,7 +3091,7 @@
       <c r="J110" s="6"/>
       <c r="K110" s="14"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:11">
       <c r="A111" s="17"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -2791,7 +3104,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="14"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:11">
       <c r="A112" s="17"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -2804,7 +3117,7 @@
       <c r="J112" s="6"/>
       <c r="K112" s="14"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:11">
       <c r="A113" s="17"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -2817,7 +3130,7 @@
       <c r="J113" s="6"/>
       <c r="K113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:11">
       <c r="A114" s="17"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -2830,7 +3143,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="14"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:11">
       <c r="A115" s="17"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -2843,7 +3156,7 @@
       <c r="J115" s="6"/>
       <c r="K115" s="14"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:11">
       <c r="A116" s="17"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -2856,7 +3169,7 @@
       <c r="J116" s="6"/>
       <c r="K116" s="14"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:11">
       <c r="A117" s="17"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -2869,7 +3182,7 @@
       <c r="J117" s="6"/>
       <c r="K117" s="14"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:11">
       <c r="A118" s="17"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -2882,7 +3195,7 @@
       <c r="J118" s="6"/>
       <c r="K118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:11">
       <c r="A119" s="17"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -2895,7 +3208,7 @@
       <c r="J119" s="6"/>
       <c r="K119" s="14"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:11">
       <c r="A120" s="17"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -2908,7 +3221,7 @@
       <c r="J120" s="6"/>
       <c r="K120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:11">
       <c r="A121" s="17"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -2921,7 +3234,7 @@
       <c r="J121" s="6"/>
       <c r="K121" s="14"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:11">
       <c r="A122" s="17"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -2934,7 +3247,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="14"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:11">
       <c r="A123" s="17"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -2947,7 +3260,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:11">
       <c r="A124" s="17"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -2960,7 +3273,7 @@
       <c r="J124" s="6"/>
       <c r="K124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:11">
       <c r="A125" s="17"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -2973,7 +3286,7 @@
       <c r="J125" s="6"/>
       <c r="K125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:11">
       <c r="A126" s="17"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -2986,7 +3299,7 @@
       <c r="J126" s="6"/>
       <c r="K126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:11">
       <c r="A127" s="17"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -2999,7 +3312,7 @@
       <c r="J127" s="6"/>
       <c r="K127" s="14"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:11">
       <c r="A128" s="17"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -3012,7 +3325,7 @@
       <c r="J128" s="6"/>
       <c r="K128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:11">
       <c r="A129" s="17"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -3025,7 +3338,7 @@
       <c r="J129" s="6"/>
       <c r="K129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:11">
       <c r="A130" s="17"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -3038,7 +3351,7 @@
       <c r="J130" s="6"/>
       <c r="K130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:11">
       <c r="A131" s="17"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -3051,7 +3364,7 @@
       <c r="J131" s="6"/>
       <c r="K131" s="14"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:11">
       <c r="A132" s="17"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -3064,7 +3377,7 @@
       <c r="J132" s="6"/>
       <c r="K132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:11">
       <c r="A133" s="17"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -3077,7 +3390,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:11">
       <c r="A134" s="17"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -3090,7 +3403,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="14"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:11">
       <c r="A135" s="17"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -3103,7 +3416,7 @@
       <c r="J135" s="6"/>
       <c r="K135" s="14"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:11">
       <c r="A136" s="17"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -3116,7 +3429,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="14"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:11">
       <c r="A137" s="17"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -3129,7 +3442,7 @@
       <c r="J137" s="6"/>
       <c r="K137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:11">
       <c r="A138" s="17"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -3142,7 +3455,7 @@
       <c r="J138" s="6"/>
       <c r="K138" s="14"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:11">
       <c r="A139" s="17"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -3155,7 +3468,7 @@
       <c r="J139" s="6"/>
       <c r="K139" s="14"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:11">
       <c r="A140" s="17"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -3168,7 +3481,7 @@
       <c r="J140" s="6"/>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:11">
       <c r="A141" s="17"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -3181,7 +3494,7 @@
       <c r="J141" s="6"/>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:11">
       <c r="A142" s="17"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -3194,7 +3507,7 @@
       <c r="J142" s="6"/>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:11">
       <c r="A143" s="17"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -3207,7 +3520,7 @@
       <c r="J143" s="6"/>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:11">
       <c r="A144" s="17"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -3220,7 +3533,7 @@
       <c r="J144" s="6"/>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:11">
       <c r="A145" s="17"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -3233,7 +3546,7 @@
       <c r="J145" s="6"/>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:11">
       <c r="A146" s="17"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -3246,7 +3559,7 @@
       <c r="J146" s="6"/>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:11">
       <c r="A147" s="17"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -3259,7 +3572,7 @@
       <c r="J147" s="6"/>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:11">
       <c r="A148" s="17"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -3272,7 +3585,7 @@
       <c r="J148" s="6"/>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:11">
       <c r="A149" s="17"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -3285,7 +3598,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:11">
       <c r="A150" s="17"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -3298,7 +3611,7 @@
       <c r="J150" s="6"/>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:11">
       <c r="A151" s="17"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -3311,7 +3624,7 @@
       <c r="J151" s="6"/>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:11">
       <c r="A152" s="17"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -3324,7 +3637,7 @@
       <c r="J152" s="6"/>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:11">
       <c r="A153" s="17"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -3337,7 +3650,7 @@
       <c r="J153" s="6"/>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:11">
       <c r="A154" s="17"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -3350,7 +3663,7 @@
       <c r="J154" s="6"/>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:11">
       <c r="A155" s="17"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -3363,7 +3676,7 @@
       <c r="J155" s="6"/>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:11">
       <c r="A156" s="17"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -3376,7 +3689,7 @@
       <c r="J156" s="6"/>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:11">
       <c r="A157" s="17"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -3389,7 +3702,7 @@
       <c r="J157" s="6"/>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:11">
       <c r="A158" s="17"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -3402,7 +3715,7 @@
       <c r="J158" s="6"/>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:11">
       <c r="A159" s="17"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -3415,7 +3728,7 @@
       <c r="J159" s="6"/>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:11">
       <c r="A160" s="17"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -3428,7 +3741,7 @@
       <c r="J160" s="6"/>
       <c r="K160" s="14"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:11">
       <c r="A161" s="17"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -3441,7 +3754,7 @@
       <c r="J161" s="6"/>
       <c r="K161" s="14"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:11">
       <c r="A162" s="17"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -3454,7 +3767,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="14"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:11">
       <c r="A163" s="17"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -3467,7 +3780,7 @@
       <c r="J163" s="6"/>
       <c r="K163" s="14"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:11">
       <c r="A164" s="17"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -3480,7 +3793,7 @@
       <c r="J164" s="6"/>
       <c r="K164" s="14"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:11">
       <c r="A165" s="17"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -3493,7 +3806,7 @@
       <c r="J165" s="6"/>
       <c r="K165" s="14"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:11">
       <c r="A166" s="17"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -3506,7 +3819,7 @@
       <c r="J166" s="6"/>
       <c r="K166" s="14"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:11">
       <c r="A167" s="17"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -3519,7 +3832,7 @@
       <c r="J167" s="6"/>
       <c r="K167" s="14"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:11">
       <c r="A168" s="17"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -3532,7 +3845,7 @@
       <c r="J168" s="6"/>
       <c r="K168" s="14"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:11">
       <c r="A169" s="17"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -3545,7 +3858,7 @@
       <c r="J169" s="6"/>
       <c r="K169" s="14"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:11">
       <c r="A170" s="17"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -3558,7 +3871,7 @@
       <c r="J170" s="6"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:11">
       <c r="A171" s="17"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -3571,7 +3884,7 @@
       <c r="J171" s="6"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:11">
       <c r="A172" s="17"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -3584,7 +3897,7 @@
       <c r="J172" s="6"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:11">
       <c r="A173" s="17"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -3597,7 +3910,7 @@
       <c r="J173" s="6"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:11">
       <c r="A174" s="17"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -3610,7 +3923,7 @@
       <c r="J174" s="6"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:11">
       <c r="A175" s="17"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -3623,7 +3936,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:11">
       <c r="A176" s="17"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -3636,7 +3949,7 @@
       <c r="J176" s="6"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:11">
       <c r="A177" s="17"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -3649,7 +3962,7 @@
       <c r="J177" s="6"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:11">
       <c r="A178" s="17"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -3662,7 +3975,7 @@
       <c r="J178" s="6"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:11">
       <c r="A179" s="17"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -3675,7 +3988,7 @@
       <c r="J179" s="6"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:11">
       <c r="A180" s="17"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -3688,7 +4001,7 @@
       <c r="J180" s="6"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:11">
       <c r="A181" s="17"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -3701,7 +4014,7 @@
       <c r="J181" s="6"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:11">
       <c r="A182" s="17"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -3714,7 +4027,7 @@
       <c r="J182" s="6"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:11">
       <c r="A183" s="17"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -3727,7 +4040,7 @@
       <c r="J183" s="6"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:11">
       <c r="A184" s="17"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -3740,7 +4053,7 @@
       <c r="J184" s="6"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:11">
       <c r="A185" s="17"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -3753,7 +4066,7 @@
       <c r="J185" s="6"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:11">
       <c r="A186" s="17"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -3766,7 +4079,7 @@
       <c r="J186" s="6"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:11">
       <c r="A187" s="17"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -3779,7 +4092,7 @@
       <c r="J187" s="6"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:11">
       <c r="A188" s="17"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -3792,7 +4105,7 @@
       <c r="J188" s="6"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:11">
       <c r="A189" s="17"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -3805,7 +4118,7 @@
       <c r="J189" s="6"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:11">
       <c r="A190" s="17"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -3818,7 +4131,7 @@
       <c r="J190" s="6"/>
       <c r="K190" s="14"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:11">
       <c r="A191" s="17"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -3831,7 +4144,7 @@
       <c r="J191" s="6"/>
       <c r="K191" s="14"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:11">
       <c r="A192" s="17"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -3844,7 +4157,7 @@
       <c r="J192" s="6"/>
       <c r="K192" s="14"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:11">
       <c r="A193" s="17"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -3857,7 +4170,7 @@
       <c r="J193" s="6"/>
       <c r="K193" s="14"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:11">
       <c r="A194" s="17"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -3870,7 +4183,7 @@
       <c r="J194" s="6"/>
       <c r="K194" s="14"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:11">
       <c r="A195" s="17"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -3883,7 +4196,7 @@
       <c r="J195" s="6"/>
       <c r="K195" s="14"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:11">
       <c r="A196" s="17"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -3896,7 +4209,7 @@
       <c r="J196" s="6"/>
       <c r="K196" s="14"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:11">
       <c r="A197" s="17"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -3909,7 +4222,7 @@
       <c r="J197" s="6"/>
       <c r="K197" s="14"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:11">
       <c r="A198" s="17"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -3922,7 +4235,7 @@
       <c r="J198" s="6"/>
       <c r="K198" s="14"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:11">
       <c r="A199" s="17"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -3935,7 +4248,7 @@
       <c r="J199" s="6"/>
       <c r="K199" s="14"/>
     </row>
-    <row r="200" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:11">
       <c r="A200" s="18"/>
       <c r="B200" s="19"/>
       <c r="C200" s="19"/>
@@ -3950,56 +4263,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:AMJ1 B2:AMJ5 L6:AMJ17 B8:K15 F17:K17 B18:AMJ21 A22:AMJ1048576">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:I7">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" dxfId="11" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K200"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AMK200"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="27.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="1" width="10.8"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5" style="1" customWidth="1"/>
+    <col min="12" max="1025" width="10.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11">
       <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
@@ -4034,8 +4339,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="n">
+    <row r="2" spans="1:11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -4067,28 +4372,28 @@
       </c>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="6">
         <v>0</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="6">
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="6">
         <v>0.02</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="6">
         <v>0</v>
       </c>
-      <c r="I3" s="13" t="n">
+      <c r="I3" s="13">
         <v>2000</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -4096,8 +4401,8 @@
       </c>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -4127,25 +4432,25 @@
       <c r="J4" s="6"/>
       <c r="K4" s="14"/>
     </row>
-    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F5" s="6">
         <v>0.2</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="6">
         <v>0</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="6">
         <v>1000</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -4154,8 +4459,8 @@
       <c r="J5" s="6"/>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+    <row r="6" spans="1:11">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -4179,16 +4484,16 @@
       <c r="J6" s="6"/>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="6">
         <v>0</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6">
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="6">
         <v>55</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -4200,8 +4505,8 @@
       <c r="J7" s="6"/>
       <c r="K7" s="14"/>
     </row>
-    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+    <row r="8" spans="1:11">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -4235,39 +4540,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:11">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="C9" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D9" s="6">
         <v>15000</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="6">
         <v>0.18</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="6">
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="6">
         <v>0</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="13">
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="6">
         <v>0</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+    <row r="10" spans="1:11">
+      <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -4301,39 +4606,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:11">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="C11" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D11" s="6">
         <v>13000</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="6">
         <v>0.18</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="6">
         <v>1</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="6">
         <v>1.67</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="13">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="6">
         <v>0</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+    <row r="12" spans="1:11">
+      <c r="A12" s="5">
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -4367,39 +4672,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:11">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="C13" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D13" s="6">
         <v>0</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="6">
         <v>0.18</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="6">
         <v>1.5</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="6">
         <v>0</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="13">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="6">
         <v>0</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+    <row r="14" spans="1:11">
+      <c r="A14" s="5">
         <v>7</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -4433,38 +4738,38 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:11">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D15" s="6" t="n">
+      <c r="C15" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D15" s="6">
         <v>10000</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="6">
         <v>0.2</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="6">
         <v>1</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="6">
         <v>0</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="13">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="6">
         <v>0</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:11">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -4477,7 +4782,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="14"/>
     </row>
-    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:11">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -4490,7 +4795,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:11">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -4503,7 +4808,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="14"/>
     </row>
-    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -4516,7 +4821,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="14"/>
     </row>
-    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -4529,7 +4834,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="14"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:11">
       <c r="A21" s="17"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -4542,7 +4847,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="14"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:11">
       <c r="A22" s="17"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -4555,7 +4860,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="14"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:11">
       <c r="A23" s="17"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -4568,7 +4873,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="14"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:11">
       <c r="A24" s="17"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -4581,7 +4886,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:11">
       <c r="A25" s="17"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -4594,7 +4899,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="14"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:11">
       <c r="A26" s="17"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -4607,7 +4912,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="14"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:11">
       <c r="A27" s="17"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -4620,7 +4925,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:11">
       <c r="A28" s="17"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -4633,7 +4938,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:11">
       <c r="A29" s="17"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -4646,7 +4951,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="14"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:11">
       <c r="A30" s="17"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4659,7 +4964,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="14"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:11">
       <c r="A31" s="17"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4672,7 +4977,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="14"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:11">
       <c r="A32" s="17"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -4685,7 +4990,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="14"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:11">
       <c r="A33" s="17"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -4698,7 +5003,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="14"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:11">
       <c r="A34" s="17"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -4711,7 +5016,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="14"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:11">
       <c r="A35" s="17"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -4724,7 +5029,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="14"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:11">
       <c r="A36" s="17"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4737,7 +5042,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="14"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:11">
       <c r="A37" s="17"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -4750,7 +5055,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="14"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:11">
       <c r="A38" s="17"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -4763,7 +5068,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="14"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:11">
       <c r="A39" s="17"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -4776,7 +5081,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="14"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:11">
       <c r="A40" s="17"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -4789,7 +5094,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="14"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:11">
       <c r="A41" s="17"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -4802,7 +5107,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="14"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:11">
       <c r="A42" s="17"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -4815,7 +5120,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="14"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:11">
       <c r="A43" s="17"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -4828,7 +5133,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="14"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:11">
       <c r="A44" s="17"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -4841,7 +5146,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="14"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:11">
       <c r="A45" s="17"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -4854,7 +5159,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="14"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:11">
       <c r="A46" s="17"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -4867,7 +5172,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="14"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:11">
       <c r="A47" s="17"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -4880,7 +5185,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="14"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:11">
       <c r="A48" s="17"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -4893,7 +5198,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="14"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:11">
       <c r="A49" s="17"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -4906,7 +5211,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="14"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:11">
       <c r="A50" s="17"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -4919,7 +5224,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="14"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:11">
       <c r="A51" s="17"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -4932,7 +5237,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="14"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:11">
       <c r="A52" s="17"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -4945,7 +5250,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="14"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:11">
       <c r="A53" s="17"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -4958,7 +5263,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="14"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:11">
       <c r="A54" s="17"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -4971,7 +5276,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="14"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:11">
       <c r="A55" s="17"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -4984,7 +5289,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="14"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:11">
       <c r="A56" s="17"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -4997,7 +5302,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="14"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:11">
       <c r="A57" s="17"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -5010,7 +5315,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="14"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:11">
       <c r="A58" s="17"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -5023,7 +5328,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="14"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:11">
       <c r="A59" s="17"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -5036,7 +5341,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="14"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:11">
       <c r="A60" s="17"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -5049,7 +5354,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="14"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:11">
       <c r="A61" s="17"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -5062,7 +5367,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="14"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:11">
       <c r="A62" s="17"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -5075,7 +5380,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="14"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:11">
       <c r="A63" s="17"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -5088,7 +5393,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="14"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:11">
       <c r="A64" s="17"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -5101,7 +5406,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="14"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:11">
       <c r="A65" s="17"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -5114,7 +5419,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="14"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:11">
       <c r="A66" s="17"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -5127,7 +5432,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="14"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:11">
       <c r="A67" s="17"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -5140,7 +5445,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="14"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:11">
       <c r="A68" s="17"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -5153,7 +5458,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="14"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:11">
       <c r="A69" s="17"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -5166,7 +5471,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:11">
       <c r="A70" s="17"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -5179,7 +5484,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="14"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:11">
       <c r="A71" s="17"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -5192,7 +5497,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:11">
       <c r="A72" s="17"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -5205,7 +5510,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="14"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:11">
       <c r="A73" s="17"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -5218,7 +5523,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="14"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:11">
       <c r="A74" s="17"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -5231,7 +5536,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="14"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:11">
       <c r="A75" s="17"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -5244,7 +5549,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="14"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:11">
       <c r="A76" s="17"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -5257,7 +5562,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="14"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:11">
       <c r="A77" s="17"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -5270,7 +5575,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="14"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:11">
       <c r="A78" s="17"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -5283,7 +5588,7 @@
       <c r="J78" s="6"/>
       <c r="K78" s="14"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:11">
       <c r="A79" s="17"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -5296,7 +5601,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="14"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:11">
       <c r="A80" s="17"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -5309,7 +5614,7 @@
       <c r="J80" s="6"/>
       <c r="K80" s="14"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:11">
       <c r="A81" s="17"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -5322,7 +5627,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="14"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:11">
       <c r="A82" s="17"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -5335,7 +5640,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="14"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:11">
       <c r="A83" s="17"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -5348,7 +5653,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="14"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:11">
       <c r="A84" s="17"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -5361,7 +5666,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="14"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:11">
       <c r="A85" s="17"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -5374,7 +5679,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="14"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:11">
       <c r="A86" s="17"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -5387,7 +5692,7 @@
       <c r="J86" s="6"/>
       <c r="K86" s="14"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:11">
       <c r="A87" s="17"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -5400,7 +5705,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="14"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:11">
       <c r="A88" s="17"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -5413,7 +5718,7 @@
       <c r="J88" s="6"/>
       <c r="K88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:11">
       <c r="A89" s="17"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -5426,7 +5731,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="14"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:11">
       <c r="A90" s="17"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -5439,7 +5744,7 @@
       <c r="J90" s="6"/>
       <c r="K90" s="14"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:11">
       <c r="A91" s="17"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -5452,7 +5757,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="14"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:11">
       <c r="A92" s="17"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -5465,7 +5770,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="14"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:11">
       <c r="A93" s="17"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -5478,7 +5783,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="14"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:11">
       <c r="A94" s="17"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -5491,7 +5796,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="14"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:11">
       <c r="A95" s="17"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -5504,7 +5809,7 @@
       <c r="J95" s="6"/>
       <c r="K95" s="14"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:11">
       <c r="A96" s="17"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -5517,7 +5822,7 @@
       <c r="J96" s="6"/>
       <c r="K96" s="14"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:11">
       <c r="A97" s="17"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -5530,7 +5835,7 @@
       <c r="J97" s="6"/>
       <c r="K97" s="14"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:11">
       <c r="A98" s="17"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -5543,7 +5848,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="14"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:11">
       <c r="A99" s="17"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -5556,7 +5861,7 @@
       <c r="J99" s="6"/>
       <c r="K99" s="14"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:11">
       <c r="A100" s="17"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -5569,7 +5874,7 @@
       <c r="J100" s="6"/>
       <c r="K100" s="14"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:11">
       <c r="A101" s="17"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -5582,7 +5887,7 @@
       <c r="J101" s="6"/>
       <c r="K101" s="14"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:11">
       <c r="A102" s="17"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -5595,7 +5900,7 @@
       <c r="J102" s="6"/>
       <c r="K102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:11">
       <c r="A103" s="17"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -5608,7 +5913,7 @@
       <c r="J103" s="6"/>
       <c r="K103" s="14"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:11">
       <c r="A104" s="17"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -5621,7 +5926,7 @@
       <c r="J104" s="6"/>
       <c r="K104" s="14"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:11">
       <c r="A105" s="17"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -5634,7 +5939,7 @@
       <c r="J105" s="6"/>
       <c r="K105" s="14"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:11">
       <c r="A106" s="17"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -5647,7 +5952,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="14"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:11">
       <c r="A107" s="17"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -5660,7 +5965,7 @@
       <c r="J107" s="6"/>
       <c r="K107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:11">
       <c r="A108" s="17"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -5673,7 +5978,7 @@
       <c r="J108" s="6"/>
       <c r="K108" s="14"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:11">
       <c r="A109" s="17"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -5686,7 +5991,7 @@
       <c r="J109" s="6"/>
       <c r="K109" s="14"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:11">
       <c r="A110" s="17"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -5699,7 +6004,7 @@
       <c r="J110" s="6"/>
       <c r="K110" s="14"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:11">
       <c r="A111" s="17"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -5712,7 +6017,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="14"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:11">
       <c r="A112" s="17"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -5725,7 +6030,7 @@
       <c r="J112" s="6"/>
       <c r="K112" s="14"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:11">
       <c r="A113" s="17"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -5738,7 +6043,7 @@
       <c r="J113" s="6"/>
       <c r="K113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:11">
       <c r="A114" s="17"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -5751,7 +6056,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="14"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:11">
       <c r="A115" s="17"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -5764,7 +6069,7 @@
       <c r="J115" s="6"/>
       <c r="K115" s="14"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:11">
       <c r="A116" s="17"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -5777,7 +6082,7 @@
       <c r="J116" s="6"/>
       <c r="K116" s="14"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:11">
       <c r="A117" s="17"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -5790,7 +6095,7 @@
       <c r="J117" s="6"/>
       <c r="K117" s="14"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:11">
       <c r="A118" s="17"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -5803,7 +6108,7 @@
       <c r="J118" s="6"/>
       <c r="K118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:11">
       <c r="A119" s="17"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -5816,7 +6121,7 @@
       <c r="J119" s="6"/>
       <c r="K119" s="14"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:11">
       <c r="A120" s="17"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -5829,7 +6134,7 @@
       <c r="J120" s="6"/>
       <c r="K120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:11">
       <c r="A121" s="17"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -5842,7 +6147,7 @@
       <c r="J121" s="6"/>
       <c r="K121" s="14"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:11">
       <c r="A122" s="17"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -5855,7 +6160,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="14"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:11">
       <c r="A123" s="17"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -5868,7 +6173,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:11">
       <c r="A124" s="17"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -5881,7 +6186,7 @@
       <c r="J124" s="6"/>
       <c r="K124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:11">
       <c r="A125" s="17"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -5894,7 +6199,7 @@
       <c r="J125" s="6"/>
       <c r="K125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:11">
       <c r="A126" s="17"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -5907,7 +6212,7 @@
       <c r="J126" s="6"/>
       <c r="K126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:11">
       <c r="A127" s="17"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -5920,7 +6225,7 @@
       <c r="J127" s="6"/>
       <c r="K127" s="14"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:11">
       <c r="A128" s="17"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -5933,7 +6238,7 @@
       <c r="J128" s="6"/>
       <c r="K128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:11">
       <c r="A129" s="17"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -5946,7 +6251,7 @@
       <c r="J129" s="6"/>
       <c r="K129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:11">
       <c r="A130" s="17"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -5959,7 +6264,7 @@
       <c r="J130" s="6"/>
       <c r="K130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:11">
       <c r="A131" s="17"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -5972,7 +6277,7 @@
       <c r="J131" s="6"/>
       <c r="K131" s="14"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:11">
       <c r="A132" s="17"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -5985,7 +6290,7 @@
       <c r="J132" s="6"/>
       <c r="K132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:11">
       <c r="A133" s="17"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -5998,7 +6303,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:11">
       <c r="A134" s="17"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -6011,7 +6316,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="14"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:11">
       <c r="A135" s="17"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -6024,7 +6329,7 @@
       <c r="J135" s="6"/>
       <c r="K135" s="14"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:11">
       <c r="A136" s="17"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -6037,7 +6342,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="14"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:11">
       <c r="A137" s="17"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -6050,7 +6355,7 @@
       <c r="J137" s="6"/>
       <c r="K137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:11">
       <c r="A138" s="17"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -6063,7 +6368,7 @@
       <c r="J138" s="6"/>
       <c r="K138" s="14"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:11">
       <c r="A139" s="17"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -6076,7 +6381,7 @@
       <c r="J139" s="6"/>
       <c r="K139" s="14"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:11">
       <c r="A140" s="17"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -6089,7 +6394,7 @@
       <c r="J140" s="6"/>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:11">
       <c r="A141" s="17"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -6102,7 +6407,7 @@
       <c r="J141" s="6"/>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:11">
       <c r="A142" s="17"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -6115,7 +6420,7 @@
       <c r="J142" s="6"/>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:11">
       <c r="A143" s="17"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -6128,7 +6433,7 @@
       <c r="J143" s="6"/>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:11">
       <c r="A144" s="17"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -6141,7 +6446,7 @@
       <c r="J144" s="6"/>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:11">
       <c r="A145" s="17"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -6154,7 +6459,7 @@
       <c r="J145" s="6"/>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:11">
       <c r="A146" s="17"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -6167,7 +6472,7 @@
       <c r="J146" s="6"/>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:11">
       <c r="A147" s="17"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -6180,7 +6485,7 @@
       <c r="J147" s="6"/>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:11">
       <c r="A148" s="17"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -6193,7 +6498,7 @@
       <c r="J148" s="6"/>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:11">
       <c r="A149" s="17"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -6206,7 +6511,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:11">
       <c r="A150" s="17"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -6219,7 +6524,7 @@
       <c r="J150" s="6"/>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:11">
       <c r="A151" s="17"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -6232,7 +6537,7 @@
       <c r="J151" s="6"/>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:11">
       <c r="A152" s="17"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -6245,7 +6550,7 @@
       <c r="J152" s="6"/>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:11">
       <c r="A153" s="17"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -6258,7 +6563,7 @@
       <c r="J153" s="6"/>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:11">
       <c r="A154" s="17"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -6271,7 +6576,7 @@
       <c r="J154" s="6"/>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:11">
       <c r="A155" s="17"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -6284,7 +6589,7 @@
       <c r="J155" s="6"/>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:11">
       <c r="A156" s="17"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -6297,7 +6602,7 @@
       <c r="J156" s="6"/>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:11">
       <c r="A157" s="17"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -6310,7 +6615,7 @@
       <c r="J157" s="6"/>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:11">
       <c r="A158" s="17"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -6323,7 +6628,7 @@
       <c r="J158" s="6"/>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:11">
       <c r="A159" s="17"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -6336,7 +6641,7 @@
       <c r="J159" s="6"/>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:11">
       <c r="A160" s="17"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -6349,7 +6654,7 @@
       <c r="J160" s="6"/>
       <c r="K160" s="14"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:11">
       <c r="A161" s="17"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -6362,7 +6667,7 @@
       <c r="J161" s="6"/>
       <c r="K161" s="14"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:11">
       <c r="A162" s="17"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -6375,7 +6680,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="14"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:11">
       <c r="A163" s="17"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -6388,7 +6693,7 @@
       <c r="J163" s="6"/>
       <c r="K163" s="14"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:11">
       <c r="A164" s="17"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -6401,7 +6706,7 @@
       <c r="J164" s="6"/>
       <c r="K164" s="14"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:11">
       <c r="A165" s="17"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -6414,7 +6719,7 @@
       <c r="J165" s="6"/>
       <c r="K165" s="14"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:11">
       <c r="A166" s="17"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -6427,7 +6732,7 @@
       <c r="J166" s="6"/>
       <c r="K166" s="14"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:11">
       <c r="A167" s="17"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -6440,7 +6745,7 @@
       <c r="J167" s="6"/>
       <c r="K167" s="14"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:11">
       <c r="A168" s="17"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -6453,7 +6758,7 @@
       <c r="J168" s="6"/>
       <c r="K168" s="14"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:11">
       <c r="A169" s="17"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -6466,7 +6771,7 @@
       <c r="J169" s="6"/>
       <c r="K169" s="14"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:11">
       <c r="A170" s="17"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -6479,7 +6784,7 @@
       <c r="J170" s="6"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:11">
       <c r="A171" s="17"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -6492,7 +6797,7 @@
       <c r="J171" s="6"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:11">
       <c r="A172" s="17"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -6505,7 +6810,7 @@
       <c r="J172" s="6"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:11">
       <c r="A173" s="17"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -6518,7 +6823,7 @@
       <c r="J173" s="6"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:11">
       <c r="A174" s="17"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -6531,7 +6836,7 @@
       <c r="J174" s="6"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:11">
       <c r="A175" s="17"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -6544,7 +6849,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:11">
       <c r="A176" s="17"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -6557,7 +6862,7 @@
       <c r="J176" s="6"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:11">
       <c r="A177" s="17"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -6570,7 +6875,7 @@
       <c r="J177" s="6"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:11">
       <c r="A178" s="17"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -6583,7 +6888,7 @@
       <c r="J178" s="6"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:11">
       <c r="A179" s="17"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -6596,7 +6901,7 @@
       <c r="J179" s="6"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:11">
       <c r="A180" s="17"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -6609,7 +6914,7 @@
       <c r="J180" s="6"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:11">
       <c r="A181" s="17"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -6622,7 +6927,7 @@
       <c r="J181" s="6"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:11">
       <c r="A182" s="17"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -6635,7 +6940,7 @@
       <c r="J182" s="6"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:11">
       <c r="A183" s="17"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -6648,7 +6953,7 @@
       <c r="J183" s="6"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:11">
       <c r="A184" s="17"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -6661,7 +6966,7 @@
       <c r="J184" s="6"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:11">
       <c r="A185" s="17"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -6674,7 +6979,7 @@
       <c r="J185" s="6"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:11">
       <c r="A186" s="17"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -6687,7 +6992,7 @@
       <c r="J186" s="6"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:11">
       <c r="A187" s="17"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -6700,7 +7005,7 @@
       <c r="J187" s="6"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:11">
       <c r="A188" s="17"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -6713,7 +7018,7 @@
       <c r="J188" s="6"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:11">
       <c r="A189" s="17"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -6726,7 +7031,7 @@
       <c r="J189" s="6"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:11">
       <c r="A190" s="17"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -6739,7 +7044,7 @@
       <c r="J190" s="6"/>
       <c r="K190" s="14"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:11">
       <c r="A191" s="17"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -6752,7 +7057,7 @@
       <c r="J191" s="6"/>
       <c r="K191" s="14"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:11">
       <c r="A192" s="17"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -6765,7 +7070,7 @@
       <c r="J192" s="6"/>
       <c r="K192" s="14"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:11">
       <c r="A193" s="17"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -6778,7 +7083,7 @@
       <c r="J193" s="6"/>
       <c r="K193" s="14"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:11">
       <c r="A194" s="17"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -6791,7 +7096,7 @@
       <c r="J194" s="6"/>
       <c r="K194" s="14"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:11">
       <c r="A195" s="17"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -6804,7 +7109,7 @@
       <c r="J195" s="6"/>
       <c r="K195" s="14"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:11">
       <c r="A196" s="17"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -6817,7 +7122,7 @@
       <c r="J196" s="6"/>
       <c r="K196" s="14"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:11">
       <c r="A197" s="17"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -6830,7 +7135,7 @@
       <c r="J197" s="6"/>
       <c r="K197" s="14"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:11">
       <c r="A198" s="17"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -6843,7 +7148,7 @@
       <c r="J198" s="6"/>
       <c r="K198" s="14"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:11">
       <c r="A199" s="17"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -6856,7 +7161,7 @@
       <c r="J199" s="6"/>
       <c r="K199" s="14"/>
     </row>
-    <row r="200" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:11">
       <c r="A200" s="18"/>
       <c r="B200" s="19"/>
       <c r="C200" s="19"/>
@@ -6871,56 +7176,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:AMJ1 B2:AMJ3 J4:AMJ4 K5:AMJ5 B6:AMJ13 L14:AMJ14 F15:AMJ21 B16:E21 A22:AMJ1048576">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K200"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:AMK200"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="27.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="1" width="10.8"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5" style="1" customWidth="1"/>
+    <col min="12" max="1025" width="10.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11">
       <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
@@ -6955,8 +7252,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="n">
+    <row r="2" spans="1:11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -6988,28 +7285,28 @@
       </c>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="6">
         <v>0</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="6">
         <v>1.8</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="6">
         <v>0.02</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I3" s="13" t="n">
+      <c r="H3" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I3" s="13">
         <v>10000</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -7017,8 +7314,8 @@
       </c>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -7048,25 +7345,25 @@
       <c r="J4" s="6"/>
       <c r="K4" s="14"/>
     </row>
-    <row r="5" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="6">
         <v>1.8</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="6">
         <v>0.5</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="G5" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H5" s="6">
         <v>3000</v>
       </c>
       <c r="I5" s="13" t="s">
@@ -7075,8 +7372,8 @@
       <c r="J5" s="6"/>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+    <row r="6" spans="1:11">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -7100,16 +7397,16 @@
       <c r="J6" s="6"/>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="6">
         <v>5000</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6">
         <v>1.8</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="6">
         <v>160</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -7121,8 +7418,8 @@
       <c r="J7" s="6"/>
       <c r="K7" s="14"/>
     </row>
-    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+    <row r="8" spans="1:11">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -7156,39 +7453,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:11">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="C9" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D9" s="6">
         <v>40000</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="6">
         <v>0.77</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="6">
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="6">
         <v>0</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="13">
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="6">
         <v>0</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+    <row r="10" spans="1:11">
+      <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -7222,39 +7519,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:11">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="C11" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D11" s="6">
         <v>38000</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="6">
         <v>0.77</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="6">
         <v>1</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="6">
         <v>1.67</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="13">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="6">
         <v>0</v>
       </c>
       <c r="K11" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+    <row r="12" spans="1:11">
+      <c r="A12" s="5">
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -7288,39 +7585,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:11">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="C13" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D13" s="6">
         <v>20000</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="6">
         <v>0.77</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="6">
         <v>1.5</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="6">
         <v>0</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="13">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="6">
         <v>0</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+    <row r="14" spans="1:11">
+      <c r="A14" s="5">
         <v>7</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -7354,38 +7651,38 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:11">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D15" s="6" t="n">
+      <c r="C15" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D15" s="6">
         <v>20000</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="6">
         <v>0.77</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="6">
         <v>1</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="6">
         <v>0</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="13">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="6">
         <v>0</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:11">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -7398,7 +7695,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="14"/>
     </row>
-    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:11">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -7411,7 +7708,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:11">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -7424,7 +7721,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="14"/>
     </row>
-    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -7437,7 +7734,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="14"/>
     </row>
-    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7450,7 +7747,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="14"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:11">
       <c r="A21" s="17"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -7463,7 +7760,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="14"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:11">
       <c r="A22" s="17"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -7476,7 +7773,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="14"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:11">
       <c r="A23" s="17"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -7489,7 +7786,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="14"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:11">
       <c r="A24" s="17"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -7502,7 +7799,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:11">
       <c r="A25" s="17"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -7515,7 +7812,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="14"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:11">
       <c r="A26" s="17"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -7528,7 +7825,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="14"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:11">
       <c r="A27" s="17"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -7541,7 +7838,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:11">
       <c r="A28" s="17"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -7554,7 +7851,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:11">
       <c r="A29" s="17"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -7567,7 +7864,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="14"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:11">
       <c r="A30" s="17"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -7580,7 +7877,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="14"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:11">
       <c r="A31" s="17"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -7593,7 +7890,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="14"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:11">
       <c r="A32" s="17"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -7606,7 +7903,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="14"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:11">
       <c r="A33" s="17"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -7619,7 +7916,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="14"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:11">
       <c r="A34" s="17"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -7632,7 +7929,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="14"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:11">
       <c r="A35" s="17"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -7645,7 +7942,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="14"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:11">
       <c r="A36" s="17"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -7658,7 +7955,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="14"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:11">
       <c r="A37" s="17"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -7671,7 +7968,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="14"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:11">
       <c r="A38" s="17"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -7684,7 +7981,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="14"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:11">
       <c r="A39" s="17"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -7697,7 +7994,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="14"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:11">
       <c r="A40" s="17"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -7710,7 +8007,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="14"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:11">
       <c r="A41" s="17"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -7723,7 +8020,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="14"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:11">
       <c r="A42" s="17"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -7736,7 +8033,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="14"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:11">
       <c r="A43" s="17"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -7749,7 +8046,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="14"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:11">
       <c r="A44" s="17"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -7762,7 +8059,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="14"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:11">
       <c r="A45" s="17"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -7775,7 +8072,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="14"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:11">
       <c r="A46" s="17"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -7788,7 +8085,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="14"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:11">
       <c r="A47" s="17"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -7801,7 +8098,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="14"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:11">
       <c r="A48" s="17"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -7814,7 +8111,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="14"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:11">
       <c r="A49" s="17"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -7827,7 +8124,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="14"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:11">
       <c r="A50" s="17"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -7840,7 +8137,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="14"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:11">
       <c r="A51" s="17"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -7853,7 +8150,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="14"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:11">
       <c r="A52" s="17"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -7866,7 +8163,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="14"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:11">
       <c r="A53" s="17"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -7879,7 +8176,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="14"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:11">
       <c r="A54" s="17"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -7892,7 +8189,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="14"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:11">
       <c r="A55" s="17"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -7905,7 +8202,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="14"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:11">
       <c r="A56" s="17"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -7918,7 +8215,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="14"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:11">
       <c r="A57" s="17"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -7931,7 +8228,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="14"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:11">
       <c r="A58" s="17"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -7944,7 +8241,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="14"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:11">
       <c r="A59" s="17"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -7957,7 +8254,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="14"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:11">
       <c r="A60" s="17"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -7970,7 +8267,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="14"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:11">
       <c r="A61" s="17"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -7983,7 +8280,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="14"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:11">
       <c r="A62" s="17"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -7996,7 +8293,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="14"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:11">
       <c r="A63" s="17"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -8009,7 +8306,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="14"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:11">
       <c r="A64" s="17"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -8022,7 +8319,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="14"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:11">
       <c r="A65" s="17"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -8035,7 +8332,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="14"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:11">
       <c r="A66" s="17"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -8048,7 +8345,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="14"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:11">
       <c r="A67" s="17"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -8061,7 +8358,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="14"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:11">
       <c r="A68" s="17"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -8074,7 +8371,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="14"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:11">
       <c r="A69" s="17"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -8087,7 +8384,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:11">
       <c r="A70" s="17"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -8100,7 +8397,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="14"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:11">
       <c r="A71" s="17"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -8113,7 +8410,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:11">
       <c r="A72" s="17"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -8126,7 +8423,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="14"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:11">
       <c r="A73" s="17"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -8139,7 +8436,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="14"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:11">
       <c r="A74" s="17"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -8152,7 +8449,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="14"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:11">
       <c r="A75" s="17"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -8165,7 +8462,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="14"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:11">
       <c r="A76" s="17"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -8178,7 +8475,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="14"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:11">
       <c r="A77" s="17"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -8191,7 +8488,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="14"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:11">
       <c r="A78" s="17"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -8204,7 +8501,7 @@
       <c r="J78" s="6"/>
       <c r="K78" s="14"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:11">
       <c r="A79" s="17"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -8217,7 +8514,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="14"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:11">
       <c r="A80" s="17"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -8230,7 +8527,7 @@
       <c r="J80" s="6"/>
       <c r="K80" s="14"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:11">
       <c r="A81" s="17"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -8243,7 +8540,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="14"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:11">
       <c r="A82" s="17"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -8256,7 +8553,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="14"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:11">
       <c r="A83" s="17"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -8269,7 +8566,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="14"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:11">
       <c r="A84" s="17"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -8282,7 +8579,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="14"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:11">
       <c r="A85" s="17"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -8295,7 +8592,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="14"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:11">
       <c r="A86" s="17"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -8308,7 +8605,7 @@
       <c r="J86" s="6"/>
       <c r="K86" s="14"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:11">
       <c r="A87" s="17"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -8321,7 +8618,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="14"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:11">
       <c r="A88" s="17"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -8334,7 +8631,7 @@
       <c r="J88" s="6"/>
       <c r="K88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:11">
       <c r="A89" s="17"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -8347,7 +8644,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="14"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:11">
       <c r="A90" s="17"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -8360,7 +8657,7 @@
       <c r="J90" s="6"/>
       <c r="K90" s="14"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:11">
       <c r="A91" s="17"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -8373,7 +8670,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="14"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:11">
       <c r="A92" s="17"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -8386,7 +8683,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="14"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:11">
       <c r="A93" s="17"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -8399,7 +8696,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="14"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:11">
       <c r="A94" s="17"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -8412,7 +8709,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="14"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:11">
       <c r="A95" s="17"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -8425,7 +8722,7 @@
       <c r="J95" s="6"/>
       <c r="K95" s="14"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:11">
       <c r="A96" s="17"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -8438,7 +8735,7 @@
       <c r="J96" s="6"/>
       <c r="K96" s="14"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:11">
       <c r="A97" s="17"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -8451,7 +8748,7 @@
       <c r="J97" s="6"/>
       <c r="K97" s="14"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:11">
       <c r="A98" s="17"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -8464,7 +8761,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="14"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:11">
       <c r="A99" s="17"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -8477,7 +8774,7 @@
       <c r="J99" s="6"/>
       <c r="K99" s="14"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:11">
       <c r="A100" s="17"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -8490,7 +8787,7 @@
       <c r="J100" s="6"/>
       <c r="K100" s="14"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:11">
       <c r="A101" s="17"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -8503,7 +8800,7 @@
       <c r="J101" s="6"/>
       <c r="K101" s="14"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:11">
       <c r="A102" s="17"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -8516,7 +8813,7 @@
       <c r="J102" s="6"/>
       <c r="K102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:11">
       <c r="A103" s="17"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -8529,7 +8826,7 @@
       <c r="J103" s="6"/>
       <c r="K103" s="14"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:11">
       <c r="A104" s="17"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -8542,7 +8839,7 @@
       <c r="J104" s="6"/>
       <c r="K104" s="14"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:11">
       <c r="A105" s="17"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -8555,7 +8852,7 @@
       <c r="J105" s="6"/>
       <c r="K105" s="14"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:11">
       <c r="A106" s="17"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -8568,7 +8865,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="14"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:11">
       <c r="A107" s="17"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -8581,7 +8878,7 @@
       <c r="J107" s="6"/>
       <c r="K107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:11">
       <c r="A108" s="17"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -8594,7 +8891,7 @@
       <c r="J108" s="6"/>
       <c r="K108" s="14"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:11">
       <c r="A109" s="17"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -8607,7 +8904,7 @@
       <c r="J109" s="6"/>
       <c r="K109" s="14"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:11">
       <c r="A110" s="17"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -8620,7 +8917,7 @@
       <c r="J110" s="6"/>
       <c r="K110" s="14"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:11">
       <c r="A111" s="17"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -8633,7 +8930,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="14"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:11">
       <c r="A112" s="17"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -8646,7 +8943,7 @@
       <c r="J112" s="6"/>
       <c r="K112" s="14"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:11">
       <c r="A113" s="17"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -8659,7 +8956,7 @@
       <c r="J113" s="6"/>
       <c r="K113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:11">
       <c r="A114" s="17"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -8672,7 +8969,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="14"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:11">
       <c r="A115" s="17"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -8685,7 +8982,7 @@
       <c r="J115" s="6"/>
       <c r="K115" s="14"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:11">
       <c r="A116" s="17"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -8698,7 +8995,7 @@
       <c r="J116" s="6"/>
       <c r="K116" s="14"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:11">
       <c r="A117" s="17"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -8711,7 +9008,7 @@
       <c r="J117" s="6"/>
       <c r="K117" s="14"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:11">
       <c r="A118" s="17"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -8724,7 +9021,7 @@
       <c r="J118" s="6"/>
       <c r="K118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:11">
       <c r="A119" s="17"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -8737,7 +9034,7 @@
       <c r="J119" s="6"/>
       <c r="K119" s="14"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:11">
       <c r="A120" s="17"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -8750,7 +9047,7 @@
       <c r="J120" s="6"/>
       <c r="K120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:11">
       <c r="A121" s="17"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -8763,7 +9060,7 @@
       <c r="J121" s="6"/>
       <c r="K121" s="14"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:11">
       <c r="A122" s="17"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -8776,7 +9073,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="14"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:11">
       <c r="A123" s="17"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -8789,7 +9086,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:11">
       <c r="A124" s="17"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -8802,7 +9099,7 @@
       <c r="J124" s="6"/>
       <c r="K124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:11">
       <c r="A125" s="17"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -8815,7 +9112,7 @@
       <c r="J125" s="6"/>
       <c r="K125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:11">
       <c r="A126" s="17"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -8828,7 +9125,7 @@
       <c r="J126" s="6"/>
       <c r="K126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:11">
       <c r="A127" s="17"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -8841,7 +9138,7 @@
       <c r="J127" s="6"/>
       <c r="K127" s="14"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:11">
       <c r="A128" s="17"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -8854,7 +9151,7 @@
       <c r="J128" s="6"/>
       <c r="K128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:11">
       <c r="A129" s="17"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -8867,7 +9164,7 @@
       <c r="J129" s="6"/>
       <c r="K129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:11">
       <c r="A130" s="17"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -8880,7 +9177,7 @@
       <c r="J130" s="6"/>
       <c r="K130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:11">
       <c r="A131" s="17"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -8893,7 +9190,7 @@
       <c r="J131" s="6"/>
       <c r="K131" s="14"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:11">
       <c r="A132" s="17"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -8906,7 +9203,7 @@
       <c r="J132" s="6"/>
       <c r="K132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:11">
       <c r="A133" s="17"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -8919,7 +9216,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:11">
       <c r="A134" s="17"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -8932,7 +9229,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="14"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:11">
       <c r="A135" s="17"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -8945,7 +9242,7 @@
       <c r="J135" s="6"/>
       <c r="K135" s="14"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:11">
       <c r="A136" s="17"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -8958,7 +9255,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="14"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:11">
       <c r="A137" s="17"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -8971,7 +9268,7 @@
       <c r="J137" s="6"/>
       <c r="K137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:11">
       <c r="A138" s="17"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -8984,7 +9281,7 @@
       <c r="J138" s="6"/>
       <c r="K138" s="14"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:11">
       <c r="A139" s="17"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -8997,7 +9294,7 @@
       <c r="J139" s="6"/>
       <c r="K139" s="14"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:11">
       <c r="A140" s="17"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -9010,7 +9307,7 @@
       <c r="J140" s="6"/>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:11">
       <c r="A141" s="17"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -9023,7 +9320,7 @@
       <c r="J141" s="6"/>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:11">
       <c r="A142" s="17"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -9036,7 +9333,7 @@
       <c r="J142" s="6"/>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:11">
       <c r="A143" s="17"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -9049,7 +9346,7 @@
       <c r="J143" s="6"/>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:11">
       <c r="A144" s="17"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -9062,7 +9359,7 @@
       <c r="J144" s="6"/>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:11">
       <c r="A145" s="17"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -9075,7 +9372,7 @@
       <c r="J145" s="6"/>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:11">
       <c r="A146" s="17"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -9088,7 +9385,7 @@
       <c r="J146" s="6"/>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:11">
       <c r="A147" s="17"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -9101,7 +9398,7 @@
       <c r="J147" s="6"/>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:11">
       <c r="A148" s="17"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -9114,7 +9411,7 @@
       <c r="J148" s="6"/>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:11">
       <c r="A149" s="17"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -9127,7 +9424,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:11">
       <c r="A150" s="17"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -9140,7 +9437,7 @@
       <c r="J150" s="6"/>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:11">
       <c r="A151" s="17"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -9153,7 +9450,7 @@
       <c r="J151" s="6"/>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:11">
       <c r="A152" s="17"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -9166,7 +9463,7 @@
       <c r="J152" s="6"/>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:11">
       <c r="A153" s="17"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -9179,7 +9476,7 @@
       <c r="J153" s="6"/>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:11">
       <c r="A154" s="17"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -9192,7 +9489,7 @@
       <c r="J154" s="6"/>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:11">
       <c r="A155" s="17"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -9205,7 +9502,7 @@
       <c r="J155" s="6"/>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:11">
       <c r="A156" s="17"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -9218,7 +9515,7 @@
       <c r="J156" s="6"/>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:11">
       <c r="A157" s="17"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -9231,7 +9528,7 @@
       <c r="J157" s="6"/>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:11">
       <c r="A158" s="17"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -9244,7 +9541,7 @@
       <c r="J158" s="6"/>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:11">
       <c r="A159" s="17"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -9257,7 +9554,7 @@
       <c r="J159" s="6"/>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:11">
       <c r="A160" s="17"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -9270,7 +9567,7 @@
       <c r="J160" s="6"/>
       <c r="K160" s="14"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:11">
       <c r="A161" s="17"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -9283,7 +9580,7 @@
       <c r="J161" s="6"/>
       <c r="K161" s="14"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:11">
       <c r="A162" s="17"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -9296,7 +9593,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="14"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:11">
       <c r="A163" s="17"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -9309,7 +9606,7 @@
       <c r="J163" s="6"/>
       <c r="K163" s="14"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:11">
       <c r="A164" s="17"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -9322,7 +9619,7 @@
       <c r="J164" s="6"/>
       <c r="K164" s="14"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:11">
       <c r="A165" s="17"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -9335,7 +9632,7 @@
       <c r="J165" s="6"/>
       <c r="K165" s="14"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:11">
       <c r="A166" s="17"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -9348,7 +9645,7 @@
       <c r="J166" s="6"/>
       <c r="K166" s="14"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:11">
       <c r="A167" s="17"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -9361,7 +9658,7 @@
       <c r="J167" s="6"/>
       <c r="K167" s="14"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:11">
       <c r="A168" s="17"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -9374,7 +9671,7 @@
       <c r="J168" s="6"/>
       <c r="K168" s="14"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:11">
       <c r="A169" s="17"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -9387,7 +9684,7 @@
       <c r="J169" s="6"/>
       <c r="K169" s="14"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:11">
       <c r="A170" s="17"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -9400,7 +9697,7 @@
       <c r="J170" s="6"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:11">
       <c r="A171" s="17"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -9413,7 +9710,7 @@
       <c r="J171" s="6"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:11">
       <c r="A172" s="17"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -9426,7 +9723,7 @@
       <c r="J172" s="6"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:11">
       <c r="A173" s="17"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -9439,7 +9736,7 @@
       <c r="J173" s="6"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:11">
       <c r="A174" s="17"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -9452,7 +9749,7 @@
       <c r="J174" s="6"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:11">
       <c r="A175" s="17"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -9465,7 +9762,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:11">
       <c r="A176" s="17"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -9478,7 +9775,7 @@
       <c r="J176" s="6"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:11">
       <c r="A177" s="17"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -9491,7 +9788,7 @@
       <c r="J177" s="6"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:11">
       <c r="A178" s="17"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -9504,7 +9801,7 @@
       <c r="J178" s="6"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:11">
       <c r="A179" s="17"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -9517,7 +9814,7 @@
       <c r="J179" s="6"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:11">
       <c r="A180" s="17"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -9530,7 +9827,7 @@
       <c r="J180" s="6"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:11">
       <c r="A181" s="17"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -9543,7 +9840,7 @@
       <c r="J181" s="6"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:11">
       <c r="A182" s="17"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -9556,7 +9853,7 @@
       <c r="J182" s="6"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:11">
       <c r="A183" s="17"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -9569,7 +9866,7 @@
       <c r="J183" s="6"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:11">
       <c r="A184" s="17"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -9582,7 +9879,7 @@
       <c r="J184" s="6"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:11">
       <c r="A185" s="17"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -9595,7 +9892,7 @@
       <c r="J185" s="6"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:11">
       <c r="A186" s="17"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -9608,7 +9905,7 @@
       <c r="J186" s="6"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:11">
       <c r="A187" s="17"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -9621,7 +9918,7 @@
       <c r="J187" s="6"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:11">
       <c r="A188" s="17"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -9634,7 +9931,7 @@
       <c r="J188" s="6"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:11">
       <c r="A189" s="17"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -9647,7 +9944,7 @@
       <c r="J189" s="6"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:11">
       <c r="A190" s="17"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -9660,7 +9957,7 @@
       <c r="J190" s="6"/>
       <c r="K190" s="14"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:11">
       <c r="A191" s="17"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -9673,7 +9970,7 @@
       <c r="J191" s="6"/>
       <c r="K191" s="14"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:11">
       <c r="A192" s="17"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -9686,7 +9983,7 @@
       <c r="J192" s="6"/>
       <c r="K192" s="14"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:11">
       <c r="A193" s="17"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -9699,7 +9996,7 @@
       <c r="J193" s="6"/>
       <c r="K193" s="14"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:11">
       <c r="A194" s="17"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -9712,7 +10009,7 @@
       <c r="J194" s="6"/>
       <c r="K194" s="14"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:11">
       <c r="A195" s="17"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -9725,7 +10022,7 @@
       <c r="J195" s="6"/>
       <c r="K195" s="14"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:11">
       <c r="A196" s="17"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -9738,7 +10035,7 @@
       <c r="J196" s="6"/>
       <c r="K196" s="14"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:11">
       <c r="A197" s="17"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -9751,7 +10048,7 @@
       <c r="J197" s="6"/>
       <c r="K197" s="14"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:11">
       <c r="A198" s="17"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -9764,7 +10061,7 @@
       <c r="J198" s="6"/>
       <c r="K198" s="14"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:11">
       <c r="A199" s="17"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -9777,7 +10074,7 @@
       <c r="J199" s="6"/>
       <c r="K199" s="14"/>
     </row>
-    <row r="200" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:11">
       <c r="A200" s="18"/>
       <c r="B200" s="19"/>
       <c r="C200" s="19"/>
@@ -9792,56 +10089,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:AMJ1 B2:AMJ4 C5:AMJ5 B6:AMJ13 L14:AMJ14 F15:AMJ21 B16:E21 A22:AMJ1048576">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:K200"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:AMK200"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="27.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="1" width="10.8"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5" style="1" customWidth="1"/>
+    <col min="12" max="1025" width="10.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11">
       <c r="A1" s="9" t="s">
         <v>25</v>
       </c>
@@ -9876,8 +10165,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="n">
+    <row r="2" spans="1:11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -9909,28 +10198,28 @@
       </c>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="6">
         <v>0</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="6">
         <v>1.2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="6">
         <v>0.08</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I3" s="6" t="n">
+      <c r="H3" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I3" s="6">
         <v>2500</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -9938,8 +10227,8 @@
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -9969,35 +10258,35 @@
       <c r="J4" s="8"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>3600</v>
+      <c r="E5" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="G5" s="6">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1000</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+    <row r="6" spans="1:11">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -10021,20 +10310,20 @@
       <c r="J6" s="8"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="6">
         <v>0</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6">
         <v>1.2</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>120</v>
+      <c r="E7" s="6">
+        <v>115</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -10042,8 +10331,8 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+    <row r="8" spans="1:11">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -10077,39 +10366,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:11">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="C9" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D9" s="6">
         <v>45000</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="6">
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I9" s="6" t="n">
+      <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="I9" s="6">
         <v>0</v>
       </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
       <c r="K9" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -10143,39 +10432,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:11">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="C11" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D11" s="6">
         <v>35000</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="F11" s="6">
         <v>1</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="I11" s="6">
         <v>0</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5">
         <v>6</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -10209,39 +10498,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:11">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="C13" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D13" s="6">
         <v>25000</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="F13" s="6">
         <v>3</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="6">
         <v>0</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="6">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="6">
         <v>0</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="5">
         <v>7</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -10275,38 +10564,38 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:11">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="6" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="D15" s="6" t="n">
+      <c r="C15" s="6">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="D15" s="6">
         <v>35000</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="F15" s="6">
         <v>1</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="6">
         <v>0</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="6">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="6">
         <v>0</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -10319,7 +10608,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="14"/>
     </row>
-    <row r="17" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:11">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -10332,7 +10621,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:11">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -10345,7 +10634,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="14"/>
     </row>
-    <row r="19" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -10358,7 +10647,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="14"/>
     </row>
-    <row r="20" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -10371,7 +10660,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="14"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:11">
       <c r="A21" s="17"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -10384,7 +10673,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="14"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:11">
       <c r="A22" s="17"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -10397,7 +10686,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="14"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:11">
       <c r="A23" s="17"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -10410,7 +10699,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="14"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:11">
       <c r="A24" s="17"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -10423,7 +10712,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:11">
       <c r="A25" s="17"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -10436,7 +10725,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="14"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:11">
       <c r="A26" s="17"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -10449,7 +10738,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="14"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:11">
       <c r="A27" s="17"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -10462,7 +10751,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:11">
       <c r="A28" s="17"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -10475,7 +10764,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:11">
       <c r="A29" s="17"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -10488,7 +10777,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="14"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:11">
       <c r="A30" s="17"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -10501,7 +10790,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="14"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:11">
       <c r="A31" s="17"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -10514,7 +10803,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="14"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:11">
       <c r="A32" s="17"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -10527,7 +10816,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="14"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:11">
       <c r="A33" s="17"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -10540,7 +10829,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="14"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:11">
       <c r="A34" s="17"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -10553,7 +10842,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="14"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:11">
       <c r="A35" s="17"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -10566,7 +10855,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="14"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:11">
       <c r="A36" s="17"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -10579,7 +10868,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="14"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:11">
       <c r="A37" s="17"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -10592,7 +10881,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="14"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:11">
       <c r="A38" s="17"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -10605,7 +10894,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="14"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:11">
       <c r="A39" s="17"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -10618,7 +10907,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="14"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:11">
       <c r="A40" s="17"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -10631,7 +10920,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="14"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:11">
       <c r="A41" s="17"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -10644,7 +10933,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="14"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:11">
       <c r="A42" s="17"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -10657,7 +10946,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="14"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:11">
       <c r="A43" s="17"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -10670,7 +10959,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="14"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:11">
       <c r="A44" s="17"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -10683,7 +10972,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="14"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:11">
       <c r="A45" s="17"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -10696,7 +10985,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="14"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:11">
       <c r="A46" s="17"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -10709,7 +10998,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="14"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:11">
       <c r="A47" s="17"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -10722,7 +11011,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="14"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:11">
       <c r="A48" s="17"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -10735,7 +11024,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="14"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:11">
       <c r="A49" s="17"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -10748,7 +11037,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="14"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:11">
       <c r="A50" s="17"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -10761,7 +11050,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="14"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:11">
       <c r="A51" s="17"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -10774,7 +11063,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="14"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:11">
       <c r="A52" s="17"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -10787,7 +11076,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="14"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:11">
       <c r="A53" s="17"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -10800,7 +11089,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="14"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:11">
       <c r="A54" s="17"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -10813,7 +11102,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="14"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:11">
       <c r="A55" s="17"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -10826,7 +11115,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="14"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:11">
       <c r="A56" s="17"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -10839,7 +11128,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="14"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:11">
       <c r="A57" s="17"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -10852,7 +11141,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="14"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:11">
       <c r="A58" s="17"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -10865,7 +11154,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="14"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:11">
       <c r="A59" s="17"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -10878,7 +11167,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="14"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:11">
       <c r="A60" s="17"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -10891,7 +11180,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="14"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:11">
       <c r="A61" s="17"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -10904,7 +11193,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="14"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:11">
       <c r="A62" s="17"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -10917,7 +11206,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="14"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:11">
       <c r="A63" s="17"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -10930,7 +11219,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="14"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:11">
       <c r="A64" s="17"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -10943,7 +11232,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="14"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:11">
       <c r="A65" s="17"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -10956,7 +11245,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="14"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:11">
       <c r="A66" s="17"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -10969,7 +11258,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="14"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:11">
       <c r="A67" s="17"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -10982,7 +11271,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="14"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:11">
       <c r="A68" s="17"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -10995,7 +11284,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="14"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:11">
       <c r="A69" s="17"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -11008,7 +11297,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="14"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:11">
       <c r="A70" s="17"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -11021,7 +11310,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="14"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:11">
       <c r="A71" s="17"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -11034,7 +11323,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="14"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:11">
       <c r="A72" s="17"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -11047,7 +11336,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="14"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:11">
       <c r="A73" s="17"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -11060,7 +11349,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="14"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:11">
       <c r="A74" s="17"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -11073,7 +11362,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="14"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:11">
       <c r="A75" s="17"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -11086,7 +11375,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="14"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:11">
       <c r="A76" s="17"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -11099,7 +11388,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="14"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:11">
       <c r="A77" s="17"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -11112,7 +11401,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="14"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:11">
       <c r="A78" s="17"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -11125,7 +11414,7 @@
       <c r="J78" s="6"/>
       <c r="K78" s="14"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:11">
       <c r="A79" s="17"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -11138,7 +11427,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="14"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:11">
       <c r="A80" s="17"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -11151,7 +11440,7 @@
       <c r="J80" s="6"/>
       <c r="K80" s="14"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:11">
       <c r="A81" s="17"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -11164,7 +11453,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="14"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:11">
       <c r="A82" s="17"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -11177,7 +11466,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="14"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:11">
       <c r="A83" s="17"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -11190,7 +11479,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="14"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:11">
       <c r="A84" s="17"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -11203,7 +11492,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="14"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:11">
       <c r="A85" s="17"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -11216,7 +11505,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="14"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:11">
       <c r="A86" s="17"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -11229,7 +11518,7 @@
       <c r="J86" s="6"/>
       <c r="K86" s="14"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:11">
       <c r="A87" s="17"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -11242,7 +11531,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="14"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:11">
       <c r="A88" s="17"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -11255,7 +11544,7 @@
       <c r="J88" s="6"/>
       <c r="K88" s="14"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:11">
       <c r="A89" s="17"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -11268,7 +11557,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="14"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:11">
       <c r="A90" s="17"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -11281,7 +11570,7 @@
       <c r="J90" s="6"/>
       <c r="K90" s="14"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:11">
       <c r="A91" s="17"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -11294,7 +11583,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="14"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:11">
       <c r="A92" s="17"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -11307,7 +11596,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="14"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:11">
       <c r="A93" s="17"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -11320,7 +11609,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="14"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:11">
       <c r="A94" s="17"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -11333,7 +11622,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="14"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:11">
       <c r="A95" s="17"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -11346,7 +11635,7 @@
       <c r="J95" s="6"/>
       <c r="K95" s="14"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:11">
       <c r="A96" s="17"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -11359,7 +11648,7 @@
       <c r="J96" s="6"/>
       <c r="K96" s="14"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:11">
       <c r="A97" s="17"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -11372,7 +11661,7 @@
       <c r="J97" s="6"/>
       <c r="K97" s="14"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:11">
       <c r="A98" s="17"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -11385,7 +11674,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="14"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:11">
       <c r="A99" s="17"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -11398,7 +11687,7 @@
       <c r="J99" s="6"/>
       <c r="K99" s="14"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:11">
       <c r="A100" s="17"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -11411,7 +11700,7 @@
       <c r="J100" s="6"/>
       <c r="K100" s="14"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:11">
       <c r="A101" s="17"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -11424,7 +11713,7 @@
       <c r="J101" s="6"/>
       <c r="K101" s="14"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:11">
       <c r="A102" s="17"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -11437,7 +11726,7 @@
       <c r="J102" s="6"/>
       <c r="K102" s="14"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:11">
       <c r="A103" s="17"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -11450,7 +11739,7 @@
       <c r="J103" s="6"/>
       <c r="K103" s="14"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:11">
       <c r="A104" s="17"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -11463,7 +11752,7 @@
       <c r="J104" s="6"/>
       <c r="K104" s="14"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:11">
       <c r="A105" s="17"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -11476,7 +11765,7 @@
       <c r="J105" s="6"/>
       <c r="K105" s="14"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:11">
       <c r="A106" s="17"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -11489,7 +11778,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="14"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:11">
       <c r="A107" s="17"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -11502,7 +11791,7 @@
       <c r="J107" s="6"/>
       <c r="K107" s="14"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:11">
       <c r="A108" s="17"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -11515,7 +11804,7 @@
       <c r="J108" s="6"/>
       <c r="K108" s="14"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:11">
       <c r="A109" s="17"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -11528,7 +11817,7 @@
       <c r="J109" s="6"/>
       <c r="K109" s="14"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:11">
       <c r="A110" s="17"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -11541,7 +11830,7 @@
       <c r="J110" s="6"/>
       <c r="K110" s="14"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:11">
       <c r="A111" s="17"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -11554,7 +11843,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="14"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:11">
       <c r="A112" s="17"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -11567,7 +11856,7 @@
       <c r="J112" s="6"/>
       <c r="K112" s="14"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:11">
       <c r="A113" s="17"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -11580,7 +11869,7 @@
       <c r="J113" s="6"/>
       <c r="K113" s="14"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:11">
       <c r="A114" s="17"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -11593,7 +11882,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="14"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:11">
       <c r="A115" s="17"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -11606,7 +11895,7 @@
       <c r="J115" s="6"/>
       <c r="K115" s="14"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:11">
       <c r="A116" s="17"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -11619,7 +11908,7 @@
       <c r="J116" s="6"/>
       <c r="K116" s="14"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:11">
       <c r="A117" s="17"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -11632,7 +11921,7 @@
       <c r="J117" s="6"/>
       <c r="K117" s="14"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:11">
       <c r="A118" s="17"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -11645,7 +11934,7 @@
       <c r="J118" s="6"/>
       <c r="K118" s="14"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:11">
       <c r="A119" s="17"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -11658,7 +11947,7 @@
       <c r="J119" s="6"/>
       <c r="K119" s="14"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:11">
       <c r="A120" s="17"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -11671,7 +11960,7 @@
       <c r="J120" s="6"/>
       <c r="K120" s="14"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:11">
       <c r="A121" s="17"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -11684,7 +11973,7 @@
       <c r="J121" s="6"/>
       <c r="K121" s="14"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:11">
       <c r="A122" s="17"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -11697,7 +11986,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="14"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:11">
       <c r="A123" s="17"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -11710,7 +11999,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="14"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:11">
       <c r="A124" s="17"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -11723,7 +12012,7 @@
       <c r="J124" s="6"/>
       <c r="K124" s="14"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:11">
       <c r="A125" s="17"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -11736,7 +12025,7 @@
       <c r="J125" s="6"/>
       <c r="K125" s="14"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:11">
       <c r="A126" s="17"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
@@ -11749,7 +12038,7 @@
       <c r="J126" s="6"/>
       <c r="K126" s="14"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:11">
       <c r="A127" s="17"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
@@ -11762,7 +12051,7 @@
       <c r="J127" s="6"/>
       <c r="K127" s="14"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:11">
       <c r="A128" s="17"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -11775,7 +12064,7 @@
       <c r="J128" s="6"/>
       <c r="K128" s="14"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:11">
       <c r="A129" s="17"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
@@ -11788,7 +12077,7 @@
       <c r="J129" s="6"/>
       <c r="K129" s="14"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:11">
       <c r="A130" s="17"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
@@ -11801,7 +12090,7 @@
       <c r="J130" s="6"/>
       <c r="K130" s="14"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:11">
       <c r="A131" s="17"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -11814,7 +12103,7 @@
       <c r="J131" s="6"/>
       <c r="K131" s="14"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:11">
       <c r="A132" s="17"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
@@ -11827,7 +12116,7 @@
       <c r="J132" s="6"/>
       <c r="K132" s="14"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:11">
       <c r="A133" s="17"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -11840,7 +12129,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="14"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:11">
       <c r="A134" s="17"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -11853,7 +12142,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="14"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:11">
       <c r="A135" s="17"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -11866,7 +12155,7 @@
       <c r="J135" s="6"/>
       <c r="K135" s="14"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:11">
       <c r="A136" s="17"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -11879,7 +12168,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="14"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:11">
       <c r="A137" s="17"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -11892,7 +12181,7 @@
       <c r="J137" s="6"/>
       <c r="K137" s="14"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:11">
       <c r="A138" s="17"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -11905,7 +12194,7 @@
       <c r="J138" s="6"/>
       <c r="K138" s="14"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:11">
       <c r="A139" s="17"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -11918,7 +12207,7 @@
       <c r="J139" s="6"/>
       <c r="K139" s="14"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:11">
       <c r="A140" s="17"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -11931,7 +12220,7 @@
       <c r="J140" s="6"/>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:11">
       <c r="A141" s="17"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -11944,7 +12233,7 @@
       <c r="J141" s="6"/>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:11">
       <c r="A142" s="17"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -11957,7 +12246,7 @@
       <c r="J142" s="6"/>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:11">
       <c r="A143" s="17"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -11970,7 +12259,7 @@
       <c r="J143" s="6"/>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:11">
       <c r="A144" s="17"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -11983,7 +12272,7 @@
       <c r="J144" s="6"/>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:11">
       <c r="A145" s="17"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -11996,7 +12285,7 @@
       <c r="J145" s="6"/>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:11">
       <c r="A146" s="17"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -12009,7 +12298,7 @@
       <c r="J146" s="6"/>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:11">
       <c r="A147" s="17"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -12022,7 +12311,7 @@
       <c r="J147" s="6"/>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:11">
       <c r="A148" s="17"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -12035,7 +12324,7 @@
       <c r="J148" s="6"/>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:11">
       <c r="A149" s="17"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -12048,7 +12337,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:11">
       <c r="A150" s="17"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -12061,7 +12350,7 @@
       <c r="J150" s="6"/>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:11">
       <c r="A151" s="17"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -12074,7 +12363,7 @@
       <c r="J151" s="6"/>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:11">
       <c r="A152" s="17"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -12087,7 +12376,7 @@
       <c r="J152" s="6"/>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:11">
       <c r="A153" s="17"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -12100,7 +12389,7 @@
       <c r="J153" s="6"/>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:11">
       <c r="A154" s="17"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -12113,7 +12402,7 @@
       <c r="J154" s="6"/>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:11">
       <c r="A155" s="17"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -12126,7 +12415,7 @@
       <c r="J155" s="6"/>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="1:11">
       <c r="A156" s="17"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -12139,7 +12428,7 @@
       <c r="J156" s="6"/>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="1:11">
       <c r="A157" s="17"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -12152,7 +12441,7 @@
       <c r="J157" s="6"/>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="1:11">
       <c r="A158" s="17"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -12165,7 +12454,7 @@
       <c r="J158" s="6"/>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" spans="1:11">
       <c r="A159" s="17"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -12178,7 +12467,7 @@
       <c r="J159" s="6"/>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" spans="1:11">
       <c r="A160" s="17"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -12191,7 +12480,7 @@
       <c r="J160" s="6"/>
       <c r="K160" s="14"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" spans="1:11">
       <c r="A161" s="17"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -12204,7 +12493,7 @@
       <c r="J161" s="6"/>
       <c r="K161" s="14"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" spans="1:11">
       <c r="A162" s="17"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -12217,7 +12506,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="14"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" spans="1:11">
       <c r="A163" s="17"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -12230,7 +12519,7 @@
       <c r="J163" s="6"/>
       <c r="K163" s="14"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" spans="1:11">
       <c r="A164" s="17"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -12243,7 +12532,7 @@
       <c r="J164" s="6"/>
       <c r="K164" s="14"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" spans="1:11">
       <c r="A165" s="17"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -12256,7 +12545,7 @@
       <c r="J165" s="6"/>
       <c r="K165" s="14"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" spans="1:11">
       <c r="A166" s="17"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -12269,7 +12558,7 @@
       <c r="J166" s="6"/>
       <c r="K166" s="14"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" spans="1:11">
       <c r="A167" s="17"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -12282,7 +12571,7 @@
       <c r="J167" s="6"/>
       <c r="K167" s="14"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" spans="1:11">
       <c r="A168" s="17"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -12295,7 +12584,7 @@
       <c r="J168" s="6"/>
       <c r="K168" s="14"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" spans="1:11">
       <c r="A169" s="17"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -12308,7 +12597,7 @@
       <c r="J169" s="6"/>
       <c r="K169" s="14"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" spans="1:11">
       <c r="A170" s="17"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
@@ -12321,7 +12610,7 @@
       <c r="J170" s="6"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" spans="1:11">
       <c r="A171" s="17"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
@@ -12334,7 +12623,7 @@
       <c r="J171" s="6"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" spans="1:11">
       <c r="A172" s="17"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
@@ -12347,7 +12636,7 @@
       <c r="J172" s="6"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" spans="1:11">
       <c r="A173" s="17"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
@@ -12360,7 +12649,7 @@
       <c r="J173" s="6"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" spans="1:11">
       <c r="A174" s="17"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
@@ -12373,7 +12662,7 @@
       <c r="J174" s="6"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" spans="1:11">
       <c r="A175" s="17"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
@@ -12386,7 +12675,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" spans="1:11">
       <c r="A176" s="17"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
@@ -12399,7 +12688,7 @@
       <c r="J176" s="6"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" spans="1:11">
       <c r="A177" s="17"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -12412,7 +12701,7 @@
       <c r="J177" s="6"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" spans="1:11">
       <c r="A178" s="17"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
@@ -12425,7 +12714,7 @@
       <c r="J178" s="6"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" spans="1:11">
       <c r="A179" s="17"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
@@ -12438,7 +12727,7 @@
       <c r="J179" s="6"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" spans="1:11">
       <c r="A180" s="17"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
@@ -12451,7 +12740,7 @@
       <c r="J180" s="6"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" spans="1:11">
       <c r="A181" s="17"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
@@ -12464,7 +12753,7 @@
       <c r="J181" s="6"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" spans="1:11">
       <c r="A182" s="17"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
@@ -12477,7 +12766,7 @@
       <c r="J182" s="6"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" spans="1:11">
       <c r="A183" s="17"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
@@ -12490,7 +12779,7 @@
       <c r="J183" s="6"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" spans="1:11">
       <c r="A184" s="17"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
@@ -12503,7 +12792,7 @@
       <c r="J184" s="6"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" spans="1:11">
       <c r="A185" s="17"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
@@ -12516,7 +12805,7 @@
       <c r="J185" s="6"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" spans="1:11">
       <c r="A186" s="17"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
@@ -12529,7 +12818,7 @@
       <c r="J186" s="6"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" spans="1:11">
       <c r="A187" s="17"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -12542,7 +12831,7 @@
       <c r="J187" s="6"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" spans="1:11">
       <c r="A188" s="17"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
@@ -12555,7 +12844,7 @@
       <c r="J188" s="6"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" spans="1:11">
       <c r="A189" s="17"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
@@ -12568,7 +12857,7 @@
       <c r="J189" s="6"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" spans="1:11">
       <c r="A190" s="17"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
@@ -12581,7 +12870,7 @@
       <c r="J190" s="6"/>
       <c r="K190" s="14"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" spans="1:11">
       <c r="A191" s="17"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
@@ -12594,7 +12883,7 @@
       <c r="J191" s="6"/>
       <c r="K191" s="14"/>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" spans="1:11">
       <c r="A192" s="17"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
@@ -12607,7 +12896,7 @@
       <c r="J192" s="6"/>
       <c r="K192" s="14"/>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" spans="1:11">
       <c r="A193" s="17"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -12620,7 +12909,7 @@
       <c r="J193" s="6"/>
       <c r="K193" s="14"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" spans="1:11">
       <c r="A194" s="17"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
@@ -12633,7 +12922,7 @@
       <c r="J194" s="6"/>
       <c r="K194" s="14"/>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" spans="1:11">
       <c r="A195" s="17"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
@@ -12646,7 +12935,7 @@
       <c r="J195" s="6"/>
       <c r="K195" s="14"/>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" spans="1:11">
       <c r="A196" s="17"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
@@ -12659,7 +12948,7 @@
       <c r="J196" s="6"/>
       <c r="K196" s="14"/>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" spans="1:11">
       <c r="A197" s="17"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
@@ -12672,7 +12961,7 @@
       <c r="J197" s="6"/>
       <c r="K197" s="14"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" spans="1:11">
       <c r="A198" s="17"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
@@ -12685,7 +12974,7 @@
       <c r="J198" s="6"/>
       <c r="K198" s="14"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" spans="1:11">
       <c r="A199" s="17"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
@@ -12698,7 +12987,7 @@
       <c r="J199" s="6"/>
       <c r="K199" s="14"/>
     </row>
-    <row r="200" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" spans="1:11">
       <c r="A200" s="18"/>
       <c r="B200" s="19"/>
       <c r="C200" s="19"/>
@@ -12712,39 +13001,34 @@
       <c r="K200" s="21"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:AMJ1 L2:AMJ15 B16:AMJ21 A22:AMJ1048576">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+  <conditionalFormatting sqref="A1:B1 D1:AMJ1 L2:AMJ15 B16:AMJ21 A22:AMJ1048576 D9:G9 I9:K9 H11">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:J7">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:K2 C3:G3 I3:K3 C4:K4 C5:F5 H5:K5 C8:K8 D9:K9 C10:K10 C12:K12 C14:K14 D15:K15 D11:K11 D13:K13">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+  <conditionalFormatting sqref="C2:K2 C3:G3 I3:K3 C4:K4 C5:F5 H5:K5 C8:K8 C10:K10 D11:K11 C12:K12 D13:K13 C14:K14 D15:K15">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Point Performance Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11288B4F-D637-47D1-BE8E-AE342F082457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECC0444-85A1-44D5-95A3-02FCD6E6C00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="B747" sheetId="4" r:id="rId4"/>
     <sheet name="JetSubmersible" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -192,10 +192,10 @@
     <t>Landing Distance 1kft</t>
   </si>
   <si>
-    <t>Max Mach (0.95) @ 35kft</t>
+    <t>Stall Velocity 88kts</t>
   </si>
   <si>
-    <t>Stall Velocity 115kts</t>
+    <t>Max Mach (0.95) @ 35kft</t>
   </si>
 </sst>
 </file>
@@ -10317,13 +10317,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="6">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E7" s="6">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -10376,7 +10376,7 @@
         <v>45000</v>
       </c>
       <c r="E9" s="6">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -10442,7 +10442,7 @@
         <v>35000</v>
       </c>
       <c r="E11" s="6">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F11" s="6">
         <v>1</v>
@@ -10508,7 +10508,7 @@
         <v>25000</v>
       </c>
       <c r="E13" s="6">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F13" s="6">
         <v>3</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -13001,7 +13001,7 @@
       <c r="K200" s="21"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:AMJ1 L2:AMJ15 B16:AMJ21 A22:AMJ1048576 D9:G9 I9:K9 H11">
+  <conditionalFormatting sqref="A1:B1 D1:AMJ1 L2:AMJ15 D9:G9 I9:K9 H11 B16:AMJ21 A22:AMJ1048576">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
+++ b/MAIN/Input Excel Sheets/Point Performance Requirements/Requirements_Input_Jet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Point Performance Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECC0444-85A1-44D5-95A3-02FCD6E6C00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A17E25C-F25B-4603-9226-E2E10BCC8D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10214,7 +10214,7 @@
         <v>1.2</v>
       </c>
       <c r="G3" s="6">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H3" s="6">
         <v>3.5000000000000003E-2</v>
